--- a/src/output/test_output.xlsx
+++ b/src/output/test_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>t</t>
   </si>
@@ -116,6 +116,24 @@
   </si>
   <si>
     <t>bus:remoteA:va_c_degree</t>
+  </si>
+  <si>
+    <t>bus:remoteB:vm_a_pu</t>
+  </si>
+  <si>
+    <t>bus:remoteB:va_a_degree</t>
+  </si>
+  <si>
+    <t>bus:remoteB:vm_b_pu</t>
+  </si>
+  <si>
+    <t>bus:remoteB:va_b_degree</t>
+  </si>
+  <si>
+    <t>bus:remoteB:vm_c_pu</t>
+  </si>
+  <si>
+    <t>bus:remoteB:va_c_degree</t>
   </si>
 </sst>
 </file>
@@ -473,10 +491,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AO22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:41">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,8 +597,26 @@
       <c r="AI1" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:41">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -686,8 +722,26 @@
       <c r="AI2">
         <v>118.3058949670522</v>
       </c>
+      <c r="AJ2">
+        <v>0.9829257148501604</v>
+      </c>
+      <c r="AK2">
+        <v>-1.600287068058186</v>
+      </c>
+      <c r="AL2">
+        <v>0.9829257148501601</v>
+      </c>
+      <c r="AM2">
+        <v>-121.6002870680582</v>
+      </c>
+      <c r="AN2">
+        <v>0.9829257148501603</v>
+      </c>
+      <c r="AO2">
+        <v>118.3997129319418</v>
+      </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:41">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -793,8 +847,26 @@
       <c r="AI3">
         <v>118.2833161815479</v>
       </c>
+      <c r="AJ3">
+        <v>0.9826903505787675</v>
+      </c>
+      <c r="AK3">
+        <v>-1.621590223844264</v>
+      </c>
+      <c r="AL3">
+        <v>0.9826903505787675</v>
+      </c>
+      <c r="AM3">
+        <v>-121.6215902238443</v>
+      </c>
+      <c r="AN3">
+        <v>0.9826903505787674</v>
+      </c>
+      <c r="AO3">
+        <v>118.3784097761557</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:41">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -900,8 +972,26 @@
       <c r="AI4">
         <v>118.2607406412221</v>
       </c>
+      <c r="AJ4">
+        <v>0.9824548803524933</v>
+      </c>
+      <c r="AK4">
+        <v>-1.642889685515492</v>
+      </c>
+      <c r="AL4">
+        <v>0.9824548803524933</v>
+      </c>
+      <c r="AM4">
+        <v>-121.6428896855155</v>
+      </c>
+      <c r="AN4">
+        <v>0.9824548803524932</v>
+      </c>
+      <c r="AO4">
+        <v>118.3571103144845</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:41">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1007,8 +1097,26 @@
       <c r="AI5">
         <v>118.2381838227807</v>
       </c>
+      <c r="AJ5">
+        <v>0.9822194658485601</v>
+      </c>
+      <c r="AK5">
+        <v>-1.664170851219349</v>
+      </c>
+      <c r="AL5">
+        <v>0.9822194658485599</v>
+      </c>
+      <c r="AM5">
+        <v>-121.6641708512194</v>
+      </c>
+      <c r="AN5">
+        <v>0.9822194658485599</v>
+      </c>
+      <c r="AO5">
+        <v>118.3358291487806</v>
+      </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:41">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1114,8 +1222,26 @@
       <c r="AI6">
         <v>118.215661215348</v>
       </c>
+      <c r="AJ6">
+        <v>0.9819842692563671</v>
+      </c>
+      <c r="AK6">
+        <v>-1.68541910912456</v>
+      </c>
+      <c r="AL6">
+        <v>0.9819842692563669</v>
+      </c>
+      <c r="AM6">
+        <v>-121.6854191091246</v>
+      </c>
+      <c r="AN6">
+        <v>0.9819842692563669</v>
+      </c>
+      <c r="AO6">
+        <v>118.3145808908754</v>
+      </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:41">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1221,8 +1347,26 @@
       <c r="AI7">
         <v>118.1931883098836</v>
       </c>
+      <c r="AJ7">
+        <v>0.9817494531658117</v>
+      </c>
+      <c r="AK7">
+        <v>-1.706619847408013</v>
+      </c>
+      <c r="AL7">
+        <v>0.9817494531658119</v>
+      </c>
+      <c r="AM7">
+        <v>-121.706619847408</v>
+      </c>
+      <c r="AN7">
+        <v>0.9817494531658119</v>
+      </c>
+      <c r="AO7">
+        <v>118.293380152592</v>
+      </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:41">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1328,8 +1472,26 @@
       <c r="AI8">
         <v>118.1707805885267</v>
       </c>
+      <c r="AJ8">
+        <v>0.9815151804538269</v>
+      </c>
+      <c r="AK8">
+        <v>-1.727758464304553</v>
+      </c>
+      <c r="AL8">
+        <v>0.981515180453827</v>
+      </c>
+      <c r="AM8">
+        <v>-121.7277584643045</v>
+      </c>
+      <c r="AN8">
+        <v>0.981515180453827</v>
+      </c>
+      <c r="AO8">
+        <v>118.2722415356954</v>
+      </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:41">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1435,8 +1597,26 @@
       <c r="AI9">
         <v>118.1484535138768</v>
       </c>
+      <c r="AJ9">
+        <v>0.9812816141691766</v>
+      </c>
+      <c r="AK9">
+        <v>-1.74882037821283</v>
+      </c>
+      <c r="AL9">
+        <v>0.9812816141691767</v>
+      </c>
+      <c r="AM9">
+        <v>-121.7488203782128</v>
+      </c>
+      <c r="AN9">
+        <v>0.9812816141691767</v>
+      </c>
+      <c r="AO9">
+        <v>118.2511796217871</v>
+      </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:41">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1542,8 +1722,26 @@
       <c r="AI10">
         <v>118.126222518216</v>
       </c>
+      <c r="AJ10">
+        <v>0.9810489174156352</v>
+      </c>
+      <c r="AK10">
+        <v>-1.769791037850871</v>
+      </c>
+      <c r="AL10">
+        <v>0.9810489174156349</v>
+      </c>
+      <c r="AM10">
+        <v>-121.7697910378509</v>
+      </c>
+      <c r="AN10">
+        <v>0.981048917415635</v>
+      </c>
+      <c r="AO10">
+        <v>118.2302089621491</v>
+      </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:41">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1649,8 +1847,26 @@
       <c r="AI11">
         <v>118.1041029926803</v>
       </c>
+      <c r="AJ11">
+        <v>0.9808172532335663</v>
+      </c>
+      <c r="AK11">
+        <v>-1.790655932454542</v>
+      </c>
+      <c r="AL11">
+        <v>0.9808172532335663</v>
+      </c>
+      <c r="AM11">
+        <v>-121.7906559324545</v>
+      </c>
+      <c r="AN11">
+        <v>0.9808172532335662</v>
+      </c>
+      <c r="AO11">
+        <v>118.2093440675454</v>
+      </c>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:41">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1756,8 +1972,26 @@
       <c r="AI12">
         <v>116.7516369243639</v>
       </c>
+      <c r="AJ12">
+        <v>0.9621563369337319</v>
+      </c>
+      <c r="AK12">
+        <v>-3.815969084416833</v>
+      </c>
+      <c r="AL12">
+        <v>0.9621563369337318</v>
+      </c>
+      <c r="AM12">
+        <v>-123.8159690844168</v>
+      </c>
+      <c r="AN12">
+        <v>0.9621563369337319</v>
+      </c>
+      <c r="AO12">
+        <v>116.1840309155832</v>
+      </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:41">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1810,7 +2044,7 @@
         <v>4.336808689942018E-19</v>
       </c>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:41">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1863,7 +2097,7 @@
         <v>4.336808689942018E-19</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:41">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1916,7 +2150,7 @@
         <v>4.336808689942018E-19</v>
       </c>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:41">
       <c r="A16" s="1">
         <v>14</v>
       </c>

--- a/src/output/test_output.xlsx
+++ b/src/output/test_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>t</t>
   </si>
@@ -46,40 +46,13 @@
     <t>ct:CT3:Ic_ka</t>
   </si>
   <si>
-    <t>line:L1:i_a_from_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_a_to_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_b_from_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_b_to_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_c_from_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_c_to_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_a_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_b_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_c_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_n_from_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_n_to_ka</t>
-  </si>
-  <si>
-    <t>line:L1:i_n_ka</t>
+    <t>cb:CB1:closed</t>
+  </si>
+  <si>
+    <t>cb:CB2:closed</t>
+  </si>
+  <si>
+    <t>cb:CB3:closed</t>
   </si>
   <si>
     <t>bus:bus1:vm_a_pu</t>
@@ -491,10 +464,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO22"/>
+  <dimension ref="A1:AF22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:41">
+    <row r="1" spans="1:32">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,35 +561,8 @@
       <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:32">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -650,98 +596,71 @@
       <c r="K2">
         <v>0.1095576497529301</v>
       </c>
-      <c r="L2">
-        <v>0.2561391940654678</v>
-      </c>
-      <c r="M2">
-        <v>0.2563747790583773</v>
-      </c>
-      <c r="N2">
-        <v>0.2561391940654678</v>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>0.2563747790583774</v>
+        <v>0.9858504635033544</v>
       </c>
       <c r="P2">
-        <v>0.2561391940654678</v>
+        <v>-1.31339081535261</v>
       </c>
       <c r="Q2">
-        <v>0.2563747790583774</v>
+        <v>0.9858504635033543</v>
       </c>
       <c r="R2">
-        <v>0.2563747790583773</v>
+        <v>-121.3133908153526</v>
       </c>
       <c r="S2">
-        <v>0.2563747790583774</v>
+        <v>0.9858504635033543</v>
       </c>
       <c r="T2">
-        <v>0.2563747790583774</v>
+        <v>118.6866091846474</v>
       </c>
       <c r="U2">
-        <v>1.942890293094024E-16</v>
+        <v>0.9818187245813159</v>
       </c>
       <c r="V2">
-        <v>1.962615573354719E-16</v>
+        <v>-1.694105032947812</v>
       </c>
       <c r="W2">
-        <v>1.962615573354719E-16</v>
+        <v>0.9818187245813159</v>
       </c>
       <c r="X2">
-        <v>0.9858504635033544</v>
+        <v>-121.6941050329478</v>
       </c>
       <c r="Y2">
-        <v>-1.31339081535261</v>
+        <v>0.9818187245813159</v>
       </c>
       <c r="Z2">
-        <v>0.9858504635033543</v>
+        <v>118.3058949670522</v>
       </c>
       <c r="AA2">
-        <v>-121.3133908153526</v>
+        <v>0.9829257148501604</v>
       </c>
       <c r="AB2">
-        <v>0.9858504635033543</v>
+        <v>-1.600287068058186</v>
       </c>
       <c r="AC2">
-        <v>118.6866091846474</v>
+        <v>0.9829257148501601</v>
       </c>
       <c r="AD2">
-        <v>0.9818187245813159</v>
+        <v>-121.6002870680582</v>
       </c>
       <c r="AE2">
-        <v>-1.694105032947812</v>
+        <v>0.9829257148501603</v>
       </c>
       <c r="AF2">
-        <v>0.9818187245813159</v>
-      </c>
-      <c r="AG2">
-        <v>-121.6941050329478</v>
-      </c>
-      <c r="AH2">
-        <v>0.9818187245813159</v>
-      </c>
-      <c r="AI2">
-        <v>118.3058949670522</v>
-      </c>
-      <c r="AJ2">
-        <v>0.9829257148501604</v>
-      </c>
-      <c r="AK2">
-        <v>-1.600287068058186</v>
-      </c>
-      <c r="AL2">
-        <v>0.9829257148501601</v>
-      </c>
-      <c r="AM2">
-        <v>-121.6002870680582</v>
-      </c>
-      <c r="AN2">
-        <v>0.9829257148501603</v>
-      </c>
-      <c r="AO2">
         <v>118.3997129319418</v>
       </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:32">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -775,98 +694,71 @@
       <c r="K3">
         <v>0.111019601312908</v>
       </c>
-      <c r="L3">
-        <v>0.2595619520660941</v>
-      </c>
-      <c r="M3">
-        <v>0.25979779585199</v>
-      </c>
-      <c r="N3">
-        <v>0.259561952066094</v>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>0.2597977958519899</v>
+        <v>0.9856544178719623</v>
       </c>
       <c r="P3">
-        <v>0.2595619520660941</v>
+        <v>-1.330814389002745</v>
       </c>
       <c r="Q3">
-        <v>0.2597977958519899</v>
+        <v>0.9856544178719624</v>
       </c>
       <c r="R3">
-        <v>0.25979779585199</v>
+        <v>-121.3308143890027</v>
       </c>
       <c r="S3">
-        <v>0.2597977958519899</v>
+        <v>0.9856544178719624</v>
       </c>
       <c r="T3">
-        <v>0.2597977958519899</v>
+        <v>118.6691856109972</v>
       </c>
       <c r="U3">
-        <v>2.220446049250313E-16</v>
+        <v>0.9815684101370595</v>
       </c>
       <c r="V3">
-        <v>2.154412023261391E-16</v>
+        <v>-1.716683818452057</v>
       </c>
       <c r="W3">
-        <v>2.220446049250313E-16</v>
+        <v>0.9815684101370594</v>
       </c>
       <c r="X3">
-        <v>0.9856544178719623</v>
+        <v>-121.7166838184521</v>
       </c>
       <c r="Y3">
-        <v>-1.330814389002745</v>
+        <v>0.9815684101370595</v>
       </c>
       <c r="Z3">
-        <v>0.9856544178719624</v>
+        <v>118.2833161815479</v>
       </c>
       <c r="AA3">
-        <v>-121.3308143890027</v>
+        <v>0.9826903505787675</v>
       </c>
       <c r="AB3">
-        <v>0.9856544178719624</v>
+        <v>-1.621590223844264</v>
       </c>
       <c r="AC3">
-        <v>118.6691856109972</v>
+        <v>0.9826903505787675</v>
       </c>
       <c r="AD3">
-        <v>0.9815684101370595</v>
+        <v>-121.6215902238443</v>
       </c>
       <c r="AE3">
-        <v>-1.716683818452057</v>
+        <v>0.9826903505787674</v>
       </c>
       <c r="AF3">
-        <v>0.9815684101370594</v>
-      </c>
-      <c r="AG3">
-        <v>-121.7166838184521</v>
-      </c>
-      <c r="AH3">
-        <v>0.9815684101370595</v>
-      </c>
-      <c r="AI3">
-        <v>118.2833161815479</v>
-      </c>
-      <c r="AJ3">
-        <v>0.9826903505787675</v>
-      </c>
-      <c r="AK3">
-        <v>-1.621590223844264</v>
-      </c>
-      <c r="AL3">
-        <v>0.9826903505787675</v>
-      </c>
-      <c r="AM3">
-        <v>-121.6215902238443</v>
-      </c>
-      <c r="AN3">
-        <v>0.9826903505787674</v>
-      </c>
-      <c r="AO3">
         <v>118.3784097761557</v>
       </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:32">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -900,98 +792,71 @@
       <c r="K4">
         <v>0.1124812816602687</v>
       </c>
-      <c r="L4">
-        <v>0.2629841386817967</v>
-      </c>
-      <c r="M4">
-        <v>0.2632202394418394</v>
-      </c>
-      <c r="N4">
-        <v>0.2629841386817968</v>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>0.2632202394418394</v>
+        <v>0.9854582635053271</v>
       </c>
       <c r="P4">
-        <v>0.2629841386817968</v>
+        <v>-1.348233401331072</v>
       </c>
       <c r="Q4">
-        <v>0.2632202394418394</v>
+        <v>0.9854582635053269</v>
       </c>
       <c r="R4">
-        <v>0.2632202394418394</v>
+        <v>-121.3482334013311</v>
       </c>
       <c r="S4">
-        <v>0.2632202394418394</v>
+        <v>0.9854582635053269</v>
       </c>
       <c r="T4">
-        <v>0.2632202394418394</v>
+        <v>118.6517665986689</v>
       </c>
       <c r="U4">
-        <v>2.423651445728339E-16</v>
+        <v>0.981317987316619</v>
       </c>
       <c r="V4">
-        <v>2.482534153247273E-16</v>
+        <v>-1.739259358777854</v>
       </c>
       <c r="W4">
-        <v>2.482534153247273E-16</v>
+        <v>0.9813179873166189</v>
       </c>
       <c r="X4">
-        <v>0.9854582635053271</v>
+        <v>-121.7392593587778</v>
       </c>
       <c r="Y4">
-        <v>-1.348233401331072</v>
+        <v>0.9813179873166187</v>
       </c>
       <c r="Z4">
-        <v>0.9854582635053269</v>
+        <v>118.2607406412221</v>
       </c>
       <c r="AA4">
-        <v>-121.3482334013311</v>
+        <v>0.9824548803524933</v>
       </c>
       <c r="AB4">
-        <v>0.9854582635053269</v>
+        <v>-1.642889685515492</v>
       </c>
       <c r="AC4">
-        <v>118.6517665986689</v>
+        <v>0.9824548803524933</v>
       </c>
       <c r="AD4">
-        <v>0.981317987316619</v>
+        <v>-121.6428896855155</v>
       </c>
       <c r="AE4">
-        <v>-1.739259358777854</v>
+        <v>0.9824548803524932</v>
       </c>
       <c r="AF4">
-        <v>0.9813179873166189</v>
-      </c>
-      <c r="AG4">
-        <v>-121.7392593587778</v>
-      </c>
-      <c r="AH4">
-        <v>0.9813179873166187</v>
-      </c>
-      <c r="AI4">
-        <v>118.2607406412221</v>
-      </c>
-      <c r="AJ4">
-        <v>0.9824548803524933</v>
-      </c>
-      <c r="AK4">
-        <v>-1.642889685515492</v>
-      </c>
-      <c r="AL4">
-        <v>0.9824548803524933</v>
-      </c>
-      <c r="AM4">
-        <v>-121.6428896855155</v>
-      </c>
-      <c r="AN4">
-        <v>0.9824548803524932</v>
-      </c>
-      <c r="AO4">
         <v>118.3571103144845</v>
       </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:32">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1025,98 +890,71 @@
       <c r="K5">
         <v>0.1139416885414792</v>
       </c>
-      <c r="L5">
-        <v>0.2664034072883419</v>
-      </c>
-      <c r="M5">
-        <v>0.2666397630972633</v>
-      </c>
-      <c r="N5">
-        <v>0.2664034072883421</v>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0.2666397630972634</v>
+        <v>0.9852621351183863</v>
       </c>
       <c r="P5">
-        <v>0.2664034072883421</v>
+        <v>-1.365635911053661</v>
       </c>
       <c r="Q5">
-        <v>0.2666397630972634</v>
+        <v>0.9852621351183865</v>
       </c>
       <c r="R5">
-        <v>0.2666397630972633</v>
+        <v>-121.3656359110537</v>
       </c>
       <c r="S5">
-        <v>0.2666397630972634</v>
+        <v>0.9852621351183862</v>
       </c>
       <c r="T5">
-        <v>0.2666397630972634</v>
+        <v>118.6343640889463</v>
       </c>
       <c r="U5">
-        <v>1.804112415015879E-16</v>
+        <v>0.9810676280528884</v>
       </c>
       <c r="V5">
-        <v>1.665334536937735E-16</v>
+        <v>-1.761816177219299</v>
       </c>
       <c r="W5">
-        <v>1.804112415015879E-16</v>
+        <v>0.9810676280528884</v>
       </c>
       <c r="X5">
-        <v>0.9852621351183863</v>
+        <v>-121.7618161772193</v>
       </c>
       <c r="Y5">
-        <v>-1.365635911053661</v>
+        <v>0.9810676280528884</v>
       </c>
       <c r="Z5">
-        <v>0.9852621351183865</v>
+        <v>118.2381838227807</v>
       </c>
       <c r="AA5">
-        <v>-121.3656359110537</v>
+        <v>0.9822194658485601</v>
       </c>
       <c r="AB5">
-        <v>0.9852621351183862</v>
+        <v>-1.664170851219349</v>
       </c>
       <c r="AC5">
-        <v>118.6343640889463</v>
+        <v>0.9822194658485599</v>
       </c>
       <c r="AD5">
-        <v>0.9810676280528884</v>
+        <v>-121.6641708512194</v>
       </c>
       <c r="AE5">
-        <v>-1.761816177219299</v>
+        <v>0.9822194658485599</v>
       </c>
       <c r="AF5">
-        <v>0.9810676280528884</v>
-      </c>
-      <c r="AG5">
-        <v>-121.7618161772193</v>
-      </c>
-      <c r="AH5">
-        <v>0.9810676280528884</v>
-      </c>
-      <c r="AI5">
-        <v>118.2381838227807</v>
-      </c>
-      <c r="AJ5">
-        <v>0.9822194658485601</v>
-      </c>
-      <c r="AK5">
-        <v>-1.664170851219349</v>
-      </c>
-      <c r="AL5">
-        <v>0.9822194658485599</v>
-      </c>
-      <c r="AM5">
-        <v>-121.6641708512194</v>
-      </c>
-      <c r="AN5">
-        <v>0.9822194658485599</v>
-      </c>
-      <c r="AO5">
         <v>118.3358291487806</v>
       </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:32">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1150,98 +988,71 @@
       <c r="K6">
         <v>0.1153998190691313</v>
       </c>
-      <c r="L6">
-        <v>0.2698174096061531</v>
-      </c>
-      <c r="M6">
-        <v>0.2700540184330826</v>
-      </c>
-      <c r="N6">
-        <v>0.269817409606153</v>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>0.2700540184330825</v>
+        <v>0.9850661679088053</v>
       </c>
       <c r="P6">
-        <v>0.2698174096061531</v>
+        <v>-1.383009972957798</v>
       </c>
       <c r="Q6">
-        <v>0.2700540184330826</v>
+        <v>0.9850661679088051</v>
       </c>
       <c r="R6">
-        <v>0.2700540184330826</v>
+        <v>-121.3830099729578</v>
       </c>
       <c r="S6">
-        <v>0.2700540184330825</v>
+        <v>0.9850661679088051</v>
       </c>
       <c r="T6">
-        <v>0.2700540184330826</v>
+        <v>118.6169900270422</v>
       </c>
       <c r="U6">
-        <v>2.914335439641036E-16</v>
+        <v>0.9808175048116948</v>
       </c>
       <c r="V6">
-        <v>2.830524433501838E-16</v>
+        <v>-1.784338784651976</v>
       </c>
       <c r="W6">
-        <v>2.914335439641036E-16</v>
+        <v>0.9808175048116947</v>
       </c>
       <c r="X6">
-        <v>0.9850661679088053</v>
+        <v>-121.784338784652</v>
       </c>
       <c r="Y6">
-        <v>-1.383009972957798</v>
+        <v>0.9808175048116945</v>
       </c>
       <c r="Z6">
-        <v>0.9850661679088051</v>
+        <v>118.215661215348</v>
       </c>
       <c r="AA6">
-        <v>-121.3830099729578</v>
+        <v>0.9819842692563671</v>
       </c>
       <c r="AB6">
-        <v>0.9850661679088051</v>
+        <v>-1.68541910912456</v>
       </c>
       <c r="AC6">
-        <v>118.6169900270422</v>
+        <v>0.9819842692563669</v>
       </c>
       <c r="AD6">
-        <v>0.9808175048116948</v>
+        <v>-121.6854191091246</v>
       </c>
       <c r="AE6">
-        <v>-1.784338784651976</v>
+        <v>0.9819842692563669</v>
       </c>
       <c r="AF6">
-        <v>0.9808175048116947</v>
-      </c>
-      <c r="AG6">
-        <v>-121.784338784652</v>
-      </c>
-      <c r="AH6">
-        <v>0.9808175048116945</v>
-      </c>
-      <c r="AI6">
-        <v>118.215661215348</v>
-      </c>
-      <c r="AJ6">
-        <v>0.9819842692563671</v>
-      </c>
-      <c r="AK6">
-        <v>-1.68541910912456</v>
-      </c>
-      <c r="AL6">
-        <v>0.9819842692563669</v>
-      </c>
-      <c r="AM6">
-        <v>-121.6854191091246</v>
-      </c>
-      <c r="AN6">
-        <v>0.9819842692563669</v>
-      </c>
-      <c r="AO6">
         <v>118.3145808908754</v>
       </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:32">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1275,98 +1086,71 @@
       <c r="K7">
         <v>0.1168546704086218</v>
       </c>
-      <c r="L7">
-        <v>0.2732237973082243</v>
-      </c>
-      <c r="M7">
-        <v>0.2734606570174363</v>
-      </c>
-      <c r="N7">
-        <v>0.2732237973082244</v>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>0.2734606570174363</v>
+        <v>0.984870497463776</v>
       </c>
       <c r="P7">
-        <v>0.2732237973082244</v>
+        <v>-1.400343646071891</v>
       </c>
       <c r="Q7">
-        <v>0.2734606570174363</v>
+        <v>0.9848704974637761</v>
       </c>
       <c r="R7">
-        <v>0.2734606570174363</v>
+        <v>-121.4003436460719</v>
       </c>
       <c r="S7">
-        <v>0.2734606570174363</v>
+        <v>0.9848704974637759</v>
       </c>
       <c r="T7">
-        <v>0.2734606570174363</v>
+        <v>118.5996563539281</v>
       </c>
       <c r="U7">
-        <v>2.830524433501838E-16</v>
+        <v>0.980567790473085</v>
       </c>
       <c r="V7">
-        <v>2.830524433501838E-16</v>
+        <v>-1.806811690116421</v>
       </c>
       <c r="W7">
-        <v>2.830524433501838E-16</v>
+        <v>0.9805677904730851</v>
       </c>
       <c r="X7">
-        <v>0.984870497463776</v>
+        <v>-121.8068116901164</v>
       </c>
       <c r="Y7">
-        <v>-1.400343646071891</v>
+        <v>0.980567790473085</v>
       </c>
       <c r="Z7">
-        <v>0.9848704974637761</v>
+        <v>118.1931883098836</v>
       </c>
       <c r="AA7">
-        <v>-121.4003436460719</v>
+        <v>0.9817494531658117</v>
       </c>
       <c r="AB7">
-        <v>0.9848704974637759</v>
+        <v>-1.706619847408013</v>
       </c>
       <c r="AC7">
-        <v>118.5996563539281</v>
+        <v>0.9817494531658119</v>
       </c>
       <c r="AD7">
-        <v>0.980567790473085</v>
+        <v>-121.706619847408</v>
       </c>
       <c r="AE7">
-        <v>-1.806811690116421</v>
+        <v>0.9817494531658119</v>
       </c>
       <c r="AF7">
-        <v>0.9805677904730851</v>
-      </c>
-      <c r="AG7">
-        <v>-121.8068116901164</v>
-      </c>
-      <c r="AH7">
-        <v>0.980567790473085</v>
-      </c>
-      <c r="AI7">
-        <v>118.1931883098836</v>
-      </c>
-      <c r="AJ7">
-        <v>0.9817494531658117</v>
-      </c>
-      <c r="AK7">
-        <v>-1.706619847408013</v>
-      </c>
-      <c r="AL7">
-        <v>0.9817494531658119</v>
-      </c>
-      <c r="AM7">
-        <v>-121.706619847408</v>
-      </c>
-      <c r="AN7">
-        <v>0.9817494531658119</v>
-      </c>
-      <c r="AO7">
         <v>118.293380152592</v>
       </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:32">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1374,124 +1158,97 @@
         <v>0.6</v>
       </c>
       <c r="C8">
-        <v>0.2768573319897339</v>
+        <v>0.3989351224990861</v>
       </c>
       <c r="D8">
-        <v>0.2768573319897339</v>
+        <v>0.398935122499086</v>
       </c>
       <c r="E8">
-        <v>0.2768573319897339</v>
+        <v>0.3989351224990861</v>
       </c>
       <c r="F8">
-        <v>0.1585637037264754</v>
+        <v>0.1597145613713661</v>
       </c>
       <c r="G8">
-        <v>0.1585637037264754</v>
+        <v>0.1597145613713661</v>
       </c>
       <c r="H8">
-        <v>0.1585637037264755</v>
+        <v>0.1597145613713661</v>
       </c>
       <c r="I8">
-        <v>0.1183052404690416</v>
+        <v>0.2392264415837599</v>
       </c>
       <c r="J8">
-        <v>0.1183052404690416</v>
+        <v>0.2392264415837599</v>
       </c>
       <c r="K8">
-        <v>0.1183052404690416</v>
-      </c>
-      <c r="L8">
-        <v>0.2766202236381283</v>
-      </c>
-      <c r="M8">
-        <v>0.2768573319897339</v>
-      </c>
-      <c r="N8">
-        <v>0.2766202236381284</v>
+        <v>0.2392264415837599</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>0.2768573319897339</v>
+        <v>0.9776533835426393</v>
       </c>
       <c r="P8">
-        <v>0.2766202236381284</v>
+        <v>-2.040798778922309</v>
       </c>
       <c r="Q8">
-        <v>0.2768573319897339</v>
+        <v>0.9776533835426393</v>
       </c>
       <c r="R8">
-        <v>0.2768573319897339</v>
+        <v>-122.0407987789223</v>
       </c>
       <c r="S8">
-        <v>0.2768573319897339</v>
+        <v>0.9776533835426391</v>
       </c>
       <c r="T8">
-        <v>0.2768573319897339</v>
+        <v>117.9592012210777</v>
       </c>
       <c r="U8">
-        <v>2.288783399261119E-16</v>
+        <v>0.9732646672060854</v>
       </c>
       <c r="V8">
-        <v>2.220446049250313E-16</v>
+        <v>-2.458350956046335</v>
       </c>
       <c r="W8">
-        <v>2.288783399261119E-16</v>
+        <v>0.9732646672060853</v>
       </c>
       <c r="X8">
-        <v>0.9846752596651933</v>
+        <v>-122.4583509560463</v>
       </c>
       <c r="Y8">
-        <v>-1.417625001875083</v>
+        <v>0.9732646672060852</v>
       </c>
       <c r="Z8">
-        <v>0.9846752596651931</v>
+        <v>117.5416490439537</v>
       </c>
       <c r="AA8">
-        <v>-121.4176250018751</v>
+        <v>0.9712240116537364</v>
       </c>
       <c r="AB8">
-        <v>0.9846752596651931</v>
+        <v>-2.671926257162932</v>
       </c>
       <c r="AC8">
-        <v>118.5823749981249</v>
+        <v>0.9712240116537363</v>
       </c>
       <c r="AD8">
-        <v>0.9803186582107546</v>
+        <v>-122.6719262571629</v>
       </c>
       <c r="AE8">
-        <v>-1.829219411473295</v>
+        <v>0.9712240116537361</v>
       </c>
       <c r="AF8">
-        <v>0.9803186582107546</v>
-      </c>
-      <c r="AG8">
-        <v>-121.8292194114733</v>
-      </c>
-      <c r="AH8">
-        <v>0.9803186582107544</v>
-      </c>
-      <c r="AI8">
-        <v>118.1707805885267</v>
-      </c>
-      <c r="AJ8">
-        <v>0.9815151804538269</v>
-      </c>
-      <c r="AK8">
-        <v>-1.727758464304553</v>
-      </c>
-      <c r="AL8">
-        <v>0.981515180453827</v>
-      </c>
-      <c r="AM8">
-        <v>-121.7277584643045</v>
-      </c>
-      <c r="AN8">
-        <v>0.981515180453827</v>
-      </c>
-      <c r="AO8">
-        <v>118.2722415356954</v>
+        <v>117.3280737428371</v>
       </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:32">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1499,124 +1256,97 @@
         <v>0.7</v>
       </c>
       <c r="C9">
-        <v>0.2802416996878186</v>
+        <v>0.15941001414414</v>
       </c>
       <c r="D9">
-        <v>0.2802416996878187</v>
+        <v>0.15941001414414</v>
       </c>
       <c r="E9">
-        <v>0.2802416996878186</v>
+        <v>0.15941001414414</v>
       </c>
       <c r="F9">
-        <v>0.1605029377957498</v>
+        <v>0.1594100141474568</v>
       </c>
       <c r="G9">
-        <v>0.1605029377957498</v>
+        <v>0.1594100141474568</v>
       </c>
       <c r="H9">
-        <v>0.1605029377957498</v>
+        <v>0.1594100141474567</v>
       </c>
       <c r="I9">
-        <v>0.1197505285977092</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.1197505285977092</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0.1197505285977091</v>
-      </c>
-      <c r="L9">
-        <v>0.2800043450372304</v>
-      </c>
-      <c r="M9">
-        <v>0.2802416996878186</v>
-      </c>
-      <c r="N9">
-        <v>0.2800043450372304</v>
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>0.2802416996878187</v>
+        <v>0.991160002998693</v>
       </c>
       <c r="P9">
-        <v>0.2800043450372304</v>
+        <v>-0.8126050944476874</v>
       </c>
       <c r="Q9">
-        <v>0.2802416996878186</v>
+        <v>0.9911600029986931</v>
       </c>
       <c r="R9">
-        <v>0.2802416996878186</v>
+        <v>-120.8126050944477</v>
       </c>
       <c r="S9">
-        <v>0.2802416996878187</v>
+        <v>0.991160002998693</v>
       </c>
       <c r="T9">
-        <v>0.2802416996878186</v>
+        <v>119.1873949055523</v>
       </c>
       <c r="U9">
-        <v>2.154412023261391E-16</v>
+        <v>0.9867801912369689</v>
       </c>
       <c r="V9">
-        <v>2.359223927328458E-16</v>
+        <v>-1.223689689051793</v>
       </c>
       <c r="W9">
-        <v>2.359223927328458E-16</v>
+        <v>0.9867801912369688</v>
       </c>
       <c r="X9">
-        <v>0.984480590593211</v>
+        <v>-121.2236896890518</v>
       </c>
       <c r="Y9">
-        <v>-1.434842132540946</v>
+        <v>0.986780191236969</v>
       </c>
       <c r="Z9">
-        <v>0.984480590593211</v>
+        <v>118.7763103109482</v>
       </c>
       <c r="AA9">
-        <v>-121.4348421325409</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.9844805905932109</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>118.565157867459</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>0.980070281369656</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>-1.85154648612315</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.9800702813696561</v>
-      </c>
-      <c r="AG9">
-        <v>-121.8515464861231</v>
-      </c>
-      <c r="AH9">
-        <v>0.980070281369656</v>
-      </c>
-      <c r="AI9">
-        <v>118.1484535138768</v>
-      </c>
-      <c r="AJ9">
-        <v>0.9812816141691766</v>
-      </c>
-      <c r="AK9">
-        <v>-1.74882037821283</v>
-      </c>
-      <c r="AL9">
-        <v>0.9812816141691767</v>
-      </c>
-      <c r="AM9">
-        <v>-121.7488203782128</v>
-      </c>
-      <c r="AN9">
-        <v>0.9812816141691767</v>
-      </c>
-      <c r="AO9">
-        <v>118.2511796217871</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:32">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1624,124 +1354,97 @@
         <v>0.8</v>
       </c>
       <c r="C10">
-        <v>0.2836114212830712</v>
+        <v>0.1613134456442891</v>
       </c>
       <c r="D10">
-        <v>0.2836114212830713</v>
+        <v>0.1613134456442892</v>
       </c>
       <c r="E10">
-        <v>0.2836114212830713</v>
+        <v>0.1613134456442892</v>
       </c>
       <c r="F10">
-        <v>0.1624338062360577</v>
+        <v>0.1613134456477266</v>
       </c>
       <c r="G10">
-        <v>0.1624338062360578</v>
+        <v>0.1613134456477267</v>
       </c>
       <c r="H10">
-        <v>0.1624338062360578</v>
+        <v>0.1613134456477266</v>
       </c>
       <c r="I10">
-        <v>0.1211895362779543</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.1211895362779544</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.1211895362779543</v>
-      </c>
-      <c r="L10">
-        <v>0.283373822779825</v>
-      </c>
-      <c r="M10">
-        <v>0.2836114212830712</v>
-      </c>
-      <c r="N10">
-        <v>0.2833738227798251</v>
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0.2836114212830713</v>
+        <v>0.9910509503245907</v>
       </c>
       <c r="P10">
-        <v>0.2833738227798251</v>
+        <v>-0.822236793493437</v>
       </c>
       <c r="Q10">
-        <v>0.2836114212830713</v>
+        <v>0.9910509503245909</v>
       </c>
       <c r="R10">
-        <v>0.2836114212830712</v>
+        <v>-120.8222367934934</v>
       </c>
       <c r="S10">
-        <v>0.2836114212830713</v>
+        <v>0.9910509503245908</v>
       </c>
       <c r="T10">
-        <v>0.2836114212830713</v>
+        <v>119.1777632065065</v>
       </c>
       <c r="U10">
-        <v>1.887583215944766E-16</v>
+        <v>0.9866184260991979</v>
       </c>
       <c r="V10">
-        <v>1.755416734288351E-16</v>
+        <v>-1.238269659606543</v>
       </c>
       <c r="W10">
-        <v>1.887583215944766E-16</v>
+        <v>0.9866184260991979</v>
       </c>
       <c r="X10">
-        <v>0.984286626428308</v>
+        <v>-121.2382696596065</v>
       </c>
       <c r="Y10">
-        <v>-1.451983159209932</v>
+        <v>0.9866184260991979</v>
       </c>
       <c r="Z10">
-        <v>0.9842866264283079</v>
+        <v>118.7617303403935</v>
       </c>
       <c r="AA10">
-        <v>-121.4519831592099</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.9842866264283079</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>118.5480168407901</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>0.9798228333419118</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>-1.873777481784032</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.9798228333419117</v>
-      </c>
-      <c r="AG10">
-        <v>-121.873777481784</v>
-      </c>
-      <c r="AH10">
-        <v>0.9798228333419117</v>
-      </c>
-      <c r="AI10">
-        <v>118.126222518216</v>
-      </c>
-      <c r="AJ10">
-        <v>0.9810489174156352</v>
-      </c>
-      <c r="AK10">
-        <v>-1.769791037850871</v>
-      </c>
-      <c r="AL10">
-        <v>0.9810489174156349</v>
-      </c>
-      <c r="AM10">
-        <v>-121.7697910378509</v>
-      </c>
-      <c r="AN10">
-        <v>0.981048917415635</v>
-      </c>
-      <c r="AO10">
-        <v>118.2302089621491</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:32">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1749,124 +1452,97 @@
         <v>0.9</v>
       </c>
       <c r="C11">
-        <v>0.2869641644225909</v>
+        <v>0.1632069527779923</v>
       </c>
       <c r="D11">
-        <v>0.2869641644225909</v>
+        <v>0.1632069527779923</v>
       </c>
       <c r="E11">
-        <v>0.2869641644225909</v>
+        <v>0.1632069527779922</v>
       </c>
       <c r="F11">
-        <v>0.164354972259278</v>
+        <v>0.1632069527815576</v>
       </c>
       <c r="G11">
-        <v>0.164354972259278</v>
+        <v>0.1632069527815576</v>
       </c>
       <c r="H11">
-        <v>0.164354972259278</v>
+        <v>0.1632069527815575</v>
       </c>
       <c r="I11">
-        <v>0.1226212678297039</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.1226212678297039</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>0.1226212678297039</v>
-      </c>
-      <c r="L11">
-        <v>0.2867263246153335</v>
-      </c>
-      <c r="M11">
-        <v>0.2869641644225909</v>
-      </c>
-      <c r="N11">
-        <v>0.2867263246153335</v>
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0.2869641644225909</v>
+        <v>0.9909424093224313</v>
       </c>
       <c r="P11">
-        <v>0.2867263246153335</v>
+        <v>-0.831817244107633</v>
       </c>
       <c r="Q11">
-        <v>0.2869641644225909</v>
+        <v>0.9909424093224316</v>
       </c>
       <c r="R11">
-        <v>0.2869641644225909</v>
+        <v>-120.8318172441076</v>
       </c>
       <c r="S11">
-        <v>0.2869641644225909</v>
+        <v>0.9909424093224314</v>
       </c>
       <c r="T11">
-        <v>0.2869641644225909</v>
+        <v>119.1681827558924</v>
       </c>
       <c r="U11">
-        <v>2.830524433501838E-16</v>
+        <v>0.9864574401396828</v>
       </c>
       <c r="V11">
-        <v>2.966732183033998E-16</v>
+        <v>-1.252773689125451</v>
       </c>
       <c r="W11">
-        <v>2.966732183033998E-16</v>
+        <v>0.9864574401396827</v>
       </c>
       <c r="X11">
-        <v>0.9840935033518702</v>
+        <v>-121.2527736891254</v>
       </c>
       <c r="Y11">
-        <v>-1.46903624028513</v>
+        <v>0.9864574401396827</v>
       </c>
       <c r="Z11">
-        <v>0.98409350335187</v>
+        <v>118.7472263108745</v>
       </c>
       <c r="AA11">
-        <v>-121.4690362402851</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.98409350335187</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>118.5309637597149</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>0.9795764874410727</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>-1.895897007319727</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.9795764874410728</v>
-      </c>
-      <c r="AG11">
-        <v>-121.8958970073197</v>
-      </c>
-      <c r="AH11">
-        <v>0.9795764874410726</v>
-      </c>
-      <c r="AI11">
-        <v>118.1041029926803</v>
-      </c>
-      <c r="AJ11">
-        <v>0.9808172532335663</v>
-      </c>
-      <c r="AK11">
-        <v>-1.790655932454542</v>
-      </c>
-      <c r="AL11">
-        <v>0.9808172532335663</v>
-      </c>
-      <c r="AM11">
-        <v>-121.7906559324545</v>
-      </c>
-      <c r="AN11">
-        <v>0.9808172532335662</v>
-      </c>
-      <c r="AO11">
-        <v>118.2093440675454</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:41">
+    <row r="12" spans="1:32">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1874,124 +1550,97 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.5373684133911436</v>
+        <v>0.1650892275134926</v>
       </c>
       <c r="D12">
-        <v>0.5373684133911436</v>
+        <v>0.1650892275134926</v>
       </c>
       <c r="E12">
-        <v>0.5373684133911437</v>
+        <v>0.1650892275134926</v>
       </c>
       <c r="F12">
-        <v>0.1684642020551825</v>
+        <v>0.1650892275171981</v>
       </c>
       <c r="G12">
-        <v>0.1684642020551824</v>
+        <v>0.1650892275171981</v>
       </c>
       <c r="H12">
-        <v>0.1684642020551825</v>
+        <v>0.1650892275171981</v>
       </c>
       <c r="I12">
-        <v>0.3691151170558544</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.3691151170558545</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0.3691151170558544</v>
-      </c>
-      <c r="L12">
-        <v>0.5371509397307913</v>
-      </c>
-      <c r="M12">
-        <v>0.5373684133911436</v>
-      </c>
-      <c r="N12">
-        <v>0.5371509397307915</v>
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>0.5373684133911436</v>
+        <v>0.9908344559245704</v>
       </c>
       <c r="P12">
-        <v>0.5371509397307914</v>
+        <v>-0.8413398450527552</v>
       </c>
       <c r="Q12">
-        <v>0.5373684133911437</v>
+        <v>0.9908344559245704</v>
       </c>
       <c r="R12">
-        <v>0.5373684133911436</v>
+        <v>-120.8413398450527</v>
       </c>
       <c r="S12">
-        <v>0.5373684133911436</v>
+        <v>0.9908344559245704</v>
       </c>
       <c r="T12">
-        <v>0.5373684133911437</v>
+        <v>119.1586601549473</v>
       </c>
       <c r="U12">
-        <v>3.510833468576701E-16</v>
+        <v>0.9862973456395486</v>
       </c>
       <c r="V12">
-        <v>3.33066907387547E-16</v>
+        <v>-1.267191757914976</v>
       </c>
       <c r="W12">
-        <v>3.510833468576701E-16</v>
+        <v>0.9862973456395487</v>
       </c>
       <c r="X12">
-        <v>0.9711957186323715</v>
+        <v>-121.267191757915</v>
       </c>
       <c r="Y12">
-        <v>-2.8050386303009</v>
+        <v>0.9862973456395486</v>
       </c>
       <c r="Z12">
-        <v>0.9711957186323715</v>
+        <v>118.732808242085</v>
       </c>
       <c r="AA12">
-        <v>-122.8050386303009</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.9711957186323714</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>117.1949613696991</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>0.9665643593388915</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>-3.248363075636163</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.9665643593388916</v>
-      </c>
-      <c r="AG12">
-        <v>-123.2483630756361</v>
-      </c>
-      <c r="AH12">
-        <v>0.9665643593388913</v>
-      </c>
-      <c r="AI12">
-        <v>116.7516369243639</v>
-      </c>
-      <c r="AJ12">
-        <v>0.9621563369337319</v>
-      </c>
-      <c r="AK12">
-        <v>-3.815969084416833</v>
-      </c>
-      <c r="AL12">
-        <v>0.9621563369337318</v>
-      </c>
-      <c r="AM12">
-        <v>-123.8159690844168</v>
-      </c>
-      <c r="AN12">
-        <v>0.9621563369337319</v>
-      </c>
-      <c r="AO12">
-        <v>116.1840309155832</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:41">
+    <row r="13" spans="1:32">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1999,52 +1648,97 @@
         <v>1.1</v>
       </c>
       <c r="C13">
-        <v>3.186385531067545E-15</v>
+        <v>0.166958968253512</v>
       </c>
       <c r="D13">
-        <v>3.186385531067545E-15</v>
+        <v>0.166958968253512</v>
       </c>
       <c r="E13">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L13">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M13">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N13">
-        <v>0.0009577089311353827</v>
+        <v>0.166958968253512</v>
+      </c>
+      <c r="F13">
+        <v>0.166958968257344</v>
+      </c>
+      <c r="G13">
+        <v>0.166958968257344</v>
+      </c>
+      <c r="H13">
+        <v>0.166958968257344</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.186385531067545E-15</v>
+        <v>0.990727165844396</v>
       </c>
       <c r="P13">
-        <v>0.0009577089311353827</v>
+        <v>-0.850798030366923</v>
       </c>
       <c r="Q13">
-        <v>3.186385531067545E-15</v>
+        <v>0.9907271658443959</v>
       </c>
       <c r="R13">
-        <v>0.0009577089311353827</v>
+        <v>-120.8507980303669</v>
       </c>
       <c r="S13">
-        <v>0.0009577089311353827</v>
+        <v>0.990727165844396</v>
       </c>
       <c r="T13">
-        <v>0.0009577089311353827</v>
+        <v>119.1492019696331</v>
       </c>
       <c r="U13">
-        <v>4.336808689942018E-19</v>
+        <v>0.9861382545021613</v>
       </c>
       <c r="V13">
-        <v>1.626278418073297E-30</v>
+        <v>-1.281513895324309</v>
       </c>
       <c r="W13">
-        <v>4.336808689942018E-19</v>
+        <v>0.9861382545021611</v>
+      </c>
+      <c r="X13">
+        <v>-121.2815138953243</v>
+      </c>
+      <c r="Y13">
+        <v>0.9861382545021612</v>
+      </c>
+      <c r="Z13">
+        <v>118.7184861046757</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:41">
+    <row r="14" spans="1:32">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2052,52 +1746,97 @@
         <v>1.2</v>
       </c>
       <c r="C14">
-        <v>3.186385531067545E-15</v>
+        <v>0.1688148807561272</v>
       </c>
       <c r="D14">
-        <v>3.186385531067545E-15</v>
+        <v>0.1688148807561272</v>
       </c>
       <c r="E14">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L14">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M14">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N14">
-        <v>0.0009577089311353827</v>
+        <v>0.1688148807561272</v>
+      </c>
+      <c r="F14">
+        <v>0.1688148807600887</v>
+      </c>
+      <c r="G14">
+        <v>0.1688148807600887</v>
+      </c>
+      <c r="H14">
+        <v>0.1688148807600887</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.186385531067545E-15</v>
+        <v>0.9906206145200305</v>
       </c>
       <c r="P14">
-        <v>0.0009577089311353827</v>
+        <v>-0.8601852739617384</v>
       </c>
       <c r="Q14">
-        <v>3.186385531067545E-15</v>
+        <v>0.9906206145200305</v>
       </c>
       <c r="R14">
-        <v>0.0009577089311353827</v>
+        <v>-120.8601852739617</v>
       </c>
       <c r="S14">
-        <v>0.0009577089311353827</v>
+        <v>0.9906206145200306</v>
       </c>
       <c r="T14">
-        <v>0.0009577089311353827</v>
+        <v>119.1398147260382</v>
       </c>
       <c r="U14">
-        <v>4.336808689942018E-19</v>
+        <v>0.9859802781708726</v>
       </c>
       <c r="V14">
-        <v>1.626278418073297E-30</v>
+        <v>-1.295730186798176</v>
       </c>
       <c r="W14">
-        <v>4.336808689942018E-19</v>
+        <v>0.9859802781708726</v>
+      </c>
+      <c r="X14">
+        <v>-121.2957301867982</v>
+      </c>
+      <c r="Y14">
+        <v>0.9859802781708725</v>
+      </c>
+      <c r="Z14">
+        <v>118.7042698132018</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:41">
+    <row r="15" spans="1:32">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2105,52 +1844,97 @@
         <v>1.3</v>
       </c>
       <c r="C15">
-        <v>3.186385531067545E-15</v>
+        <v>0.1706556790541588</v>
       </c>
       <c r="D15">
-        <v>3.186385531067545E-15</v>
+        <v>0.1706556790541588</v>
       </c>
       <c r="E15">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L15">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M15">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N15">
-        <v>0.0009577089311353827</v>
+        <v>0.1706556790541588</v>
+      </c>
+      <c r="F15">
+        <v>0.1706556790582643</v>
+      </c>
+      <c r="G15">
+        <v>0.1706556790582643</v>
+      </c>
+      <c r="H15">
+        <v>0.1706556790582643</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.186385531067545E-15</v>
+        <v>0.9905148770577104</v>
       </c>
       <c r="P15">
-        <v>0.0009577089311353827</v>
+        <v>-0.8694950942052618</v>
       </c>
       <c r="Q15">
-        <v>3.186385531067545E-15</v>
+        <v>0.9905148770577102</v>
       </c>
       <c r="R15">
-        <v>0.0009577089311353827</v>
+        <v>-120.8694950942052</v>
       </c>
       <c r="S15">
-        <v>0.0009577089311353827</v>
+        <v>0.9905148770577102</v>
       </c>
       <c r="T15">
-        <v>0.0009577089311353827</v>
+        <v>119.1305049057947</v>
       </c>
       <c r="U15">
-        <v>4.336808689942018E-19</v>
+        <v>0.9858235275464586</v>
       </c>
       <c r="V15">
-        <v>1.626278418073297E-30</v>
+        <v>-1.309830780919289</v>
       </c>
       <c r="W15">
-        <v>4.336808689942018E-19</v>
+        <v>0.9858235275464586</v>
+      </c>
+      <c r="X15">
+        <v>-121.3098307809193</v>
+      </c>
+      <c r="Y15">
+        <v>0.9858235275464585</v>
+      </c>
+      <c r="Z15">
+        <v>118.6901692190807</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:41">
+    <row r="16" spans="1:32">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2158,52 +1942,97 @@
         <v>1.4</v>
       </c>
       <c r="C16">
-        <v>3.186385531067545E-15</v>
+        <v>0.1724800863724269</v>
       </c>
       <c r="D16">
-        <v>3.186385531067545E-15</v>
+        <v>0.172480086372427</v>
       </c>
       <c r="E16">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L16">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M16">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N16">
-        <v>0.0009577089311353827</v>
+        <v>0.172480086372427</v>
+      </c>
+      <c r="F16">
+        <v>0.1724800863766686</v>
+      </c>
+      <c r="G16">
+        <v>0.1724800863766686</v>
+      </c>
+      <c r="H16">
+        <v>0.1724800863766686</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.186385531067545E-15</v>
+        <v>0.9904100281748831</v>
       </c>
       <c r="P16">
-        <v>0.0009577089311353827</v>
+        <v>-0.8787210584866907</v>
       </c>
       <c r="Q16">
-        <v>3.186385531067545E-15</v>
+        <v>0.9904100281748831</v>
       </c>
       <c r="R16">
-        <v>0.0009577089311353827</v>
+        <v>-120.8787210584867</v>
       </c>
       <c r="S16">
-        <v>0.0009577089311353827</v>
+        <v>0.9904100281748831</v>
       </c>
       <c r="T16">
-        <v>0.0009577089311353827</v>
+        <v>119.1212789415133</v>
       </c>
       <c r="U16">
-        <v>4.336808689942018E-19</v>
+        <v>0.9856681129042683</v>
       </c>
       <c r="V16">
-        <v>1.626278418073297E-30</v>
+        <v>-1.323805896435099</v>
       </c>
       <c r="W16">
-        <v>4.336808689942018E-19</v>
+        <v>0.9856681129042681</v>
+      </c>
+      <c r="X16">
+        <v>-121.3238058964351</v>
+      </c>
+      <c r="Y16">
+        <v>0.9856681129042681</v>
+      </c>
+      <c r="Z16">
+        <v>118.6761941035649</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:32">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2211,52 +2040,97 @@
         <v>1.5</v>
       </c>
       <c r="C17">
-        <v>3.186385531067545E-15</v>
+        <v>0.1742868360420642</v>
       </c>
       <c r="D17">
-        <v>3.186385531067545E-15</v>
+        <v>0.1742868360420643</v>
       </c>
       <c r="E17">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L17">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M17">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N17">
-        <v>0.0009577089311353827</v>
+        <v>0.1742868360420643</v>
+      </c>
+      <c r="F17">
+        <v>0.174286836046442</v>
+      </c>
+      <c r="G17">
+        <v>0.1742868360464422</v>
+      </c>
+      <c r="H17">
+        <v>0.1742868360464421</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.186385531067545E-15</v>
+        <v>0.9903061421431014</v>
       </c>
       <c r="P17">
-        <v>0.0009577089311353827</v>
+        <v>-0.8878567877593436</v>
       </c>
       <c r="Q17">
-        <v>3.186385531067545E-15</v>
+        <v>0.9903061421431013</v>
       </c>
       <c r="R17">
-        <v>0.0009577089311353827</v>
+        <v>-120.8878567877593</v>
       </c>
       <c r="S17">
-        <v>0.0009577089311353827</v>
+        <v>0.9903061421431013</v>
       </c>
       <c r="T17">
-        <v>0.0009577089311353827</v>
+        <v>119.1121432122407</v>
       </c>
       <c r="U17">
-        <v>4.336808689942018E-19</v>
+        <v>0.9855141438111965</v>
       </c>
       <c r="V17">
-        <v>1.626278418073297E-30</v>
+        <v>-1.337645829263395</v>
       </c>
       <c r="W17">
-        <v>4.336808689942018E-19</v>
+        <v>0.9855141438111963</v>
+      </c>
+      <c r="X17">
+        <v>-121.3376458292634</v>
+      </c>
+      <c r="Y17">
+        <v>0.9855141438111964</v>
+      </c>
+      <c r="Z17">
+        <v>118.6623541707366</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:32">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2264,52 +2138,97 @@
         <v>1.6</v>
       </c>
       <c r="C18">
-        <v>3.186385531067545E-15</v>
+        <v>0.1760746724113036</v>
       </c>
       <c r="D18">
-        <v>3.186385531067545E-15</v>
+        <v>0.1760746724113036</v>
       </c>
       <c r="E18">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L18">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M18">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N18">
-        <v>0.0009577089311353827</v>
+        <v>0.1760746724113036</v>
+      </c>
+      <c r="F18">
+        <v>0.1760746724158245</v>
+      </c>
+      <c r="G18">
+        <v>0.1760746724158245</v>
+      </c>
+      <c r="H18">
+        <v>0.1760746724158245</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.186385531067545E-15</v>
+        <v>0.9902032927307285</v>
       </c>
       <c r="P18">
-        <v>0.0009577089311353827</v>
+        <v>-0.8968959610586459</v>
       </c>
       <c r="Q18">
-        <v>3.186385531067545E-15</v>
+        <v>0.9902032927307284</v>
       </c>
       <c r="R18">
-        <v>0.0009577089311353827</v>
+        <v>-120.8968959610586</v>
       </c>
       <c r="S18">
-        <v>0.0009577089311353827</v>
+        <v>0.9902032927307285</v>
       </c>
       <c r="T18">
-        <v>0.0009577089311353827</v>
+        <v>119.1031040389413</v>
       </c>
       <c r="U18">
-        <v>4.336808689942018E-19</v>
+        <v>0.9853617290425237</v>
       </c>
       <c r="V18">
-        <v>1.626278418073297E-30</v>
+        <v>-1.351340959471384</v>
       </c>
       <c r="W18">
-        <v>4.336808689942018E-19</v>
+        <v>0.9853617290425238</v>
+      </c>
+      <c r="X18">
+        <v>-121.3513409594714</v>
+      </c>
+      <c r="Y18">
+        <v>0.9853617290425237</v>
+      </c>
+      <c r="Z18">
+        <v>118.6486590405286</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:32">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2317,52 +2236,97 @@
         <v>1.7</v>
       </c>
       <c r="C19">
-        <v>3.186385531067545E-15</v>
+        <v>0.1778423517518909</v>
       </c>
       <c r="D19">
-        <v>3.186385531067545E-15</v>
+        <v>0.1778423517518909</v>
       </c>
       <c r="E19">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L19">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M19">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N19">
-        <v>0.0009577089311353827</v>
+        <v>0.1778423517518909</v>
+      </c>
+      <c r="F19">
+        <v>0.1778423517565471</v>
+      </c>
+      <c r="G19">
+        <v>0.1778423517565471</v>
+      </c>
+      <c r="H19">
+        <v>0.1778423517565471</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.186385531067545E-15</v>
+        <v>0.9901015531455419</v>
       </c>
       <c r="P19">
-        <v>0.0009577089311353827</v>
+        <v>-0.9058323199913475</v>
       </c>
       <c r="Q19">
-        <v>3.186385531067545E-15</v>
+        <v>0.9901015531455418</v>
       </c>
       <c r="R19">
-        <v>0.0009577089311353827</v>
+        <v>-120.9058323199914</v>
       </c>
       <c r="S19">
-        <v>0.0009577089311353827</v>
+        <v>0.9901015531455416</v>
       </c>
       <c r="T19">
-        <v>0.0009577089311353827</v>
+        <v>119.0941676800087</v>
       </c>
       <c r="U19">
-        <v>4.336808689942018E-19</v>
+        <v>0.9852109764987288</v>
       </c>
       <c r="V19">
-        <v>1.626278418073297E-30</v>
+        <v>-1.364881758222389</v>
       </c>
       <c r="W19">
-        <v>4.336808689942018E-19</v>
+        <v>0.9852109764987287</v>
+      </c>
+      <c r="X19">
+        <v>-121.3648817582224</v>
+      </c>
+      <c r="Y19">
+        <v>0.9852109764987287</v>
+      </c>
+      <c r="Z19">
+        <v>118.6351182417776</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:32">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2370,52 +2334,97 @@
         <v>1.8</v>
       </c>
       <c r="C20">
-        <v>3.186385531067545E-15</v>
+        <v>0.1795886431604491</v>
       </c>
       <c r="D20">
-        <v>3.186385531067545E-15</v>
+        <v>0.1795886431604492</v>
       </c>
       <c r="E20">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L20">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M20">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N20">
-        <v>0.0009577089311353827</v>
+        <v>0.1795886431604492</v>
+      </c>
+      <c r="F20">
+        <v>0.1795886431652393</v>
+      </c>
+      <c r="G20">
+        <v>0.1795886431652395</v>
+      </c>
+      <c r="H20">
+        <v>0.1795886431652394</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.186385531067545E-15</v>
+        <v>0.9900009959772811</v>
       </c>
       <c r="P20">
-        <v>0.0009577089311353827</v>
+        <v>-0.9146596731929871</v>
       </c>
       <c r="Q20">
-        <v>3.186385531067545E-15</v>
+        <v>0.990000995977281</v>
       </c>
       <c r="R20">
-        <v>0.0009577089311353827</v>
+        <v>-120.914659673193</v>
       </c>
       <c r="S20">
-        <v>0.0009577089311353827</v>
+        <v>0.990000995977281</v>
       </c>
       <c r="T20">
-        <v>0.0009577089311353827</v>
+        <v>119.085340326807</v>
       </c>
       <c r="U20">
-        <v>4.336808689942018E-19</v>
+        <v>0.9850619931223308</v>
       </c>
       <c r="V20">
-        <v>1.626278418073297E-30</v>
+        <v>-1.378258794684954</v>
       </c>
       <c r="W20">
-        <v>4.336808689942018E-19</v>
+        <v>0.9850619931223307</v>
+      </c>
+      <c r="X20">
+        <v>-121.3782587946849</v>
+      </c>
+      <c r="Y20">
+        <v>0.9850619931223307</v>
+      </c>
+      <c r="Z20">
+        <v>118.621741205315</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:32">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2423,52 +2432,97 @@
         <v>1.9</v>
       </c>
       <c r="C21">
-        <v>3.186385531067545E-15</v>
+        <v>0.1813123294540719</v>
       </c>
       <c r="D21">
-        <v>3.186385531067545E-15</v>
+        <v>0.1813123294540719</v>
       </c>
       <c r="E21">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L21">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M21">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N21">
-        <v>0.0009577089311353827</v>
+        <v>0.181312329454072</v>
+      </c>
+      <c r="F21">
+        <v>0.1813123294590102</v>
+      </c>
+      <c r="G21">
+        <v>0.1813123294590102</v>
+      </c>
+      <c r="H21">
+        <v>0.1813123294590102</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.186385531067545E-15</v>
+        <v>0.9899016931401919</v>
       </c>
       <c r="P21">
-        <v>0.0009577089311353827</v>
+        <v>-0.9233719007497385</v>
       </c>
       <c r="Q21">
-        <v>3.186385531067545E-15</v>
+        <v>0.9899016931401918</v>
       </c>
       <c r="R21">
-        <v>0.0009577089311353827</v>
+        <v>-120.9233719007497</v>
       </c>
       <c r="S21">
-        <v>0.0009577089311353827</v>
+        <v>0.9899016931401919</v>
       </c>
       <c r="T21">
-        <v>0.0009577089311353827</v>
+        <v>119.0766280992503</v>
       </c>
       <c r="U21">
-        <v>4.336808689942018E-19</v>
+        <v>0.984914884814846</v>
       </c>
       <c r="V21">
-        <v>1.626278418073297E-30</v>
+        <v>-1.391462742898403</v>
       </c>
       <c r="W21">
-        <v>4.336808689942018E-19</v>
+        <v>0.9849148848148458</v>
+      </c>
+      <c r="X21">
+        <v>-121.3914627428984</v>
+      </c>
+      <c r="Y21">
+        <v>0.9849148848148459</v>
+      </c>
+      <c r="Z21">
+        <v>118.6085372571016</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:32">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2476,49 +2530,94 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>3.186385531067545E-15</v>
+        <v>0.183012208059325</v>
       </c>
       <c r="D22">
-        <v>3.186385531067545E-15</v>
+        <v>0.183012208059325</v>
       </c>
       <c r="E22">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="L22">
-        <v>0.0009577089311353827</v>
-      </c>
-      <c r="M22">
-        <v>3.186385531067545E-15</v>
-      </c>
-      <c r="N22">
-        <v>0.0009577089311353827</v>
+        <v>0.183012208059325</v>
+      </c>
+      <c r="F22">
+        <v>0.1830122080644054</v>
+      </c>
+      <c r="G22">
+        <v>0.1830122080644054</v>
+      </c>
+      <c r="H22">
+        <v>0.1830122080644054</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.186385531067545E-15</v>
+        <v>0.9898037158156341</v>
       </c>
       <c r="P22">
-        <v>0.0009577089311353827</v>
+        <v>-0.9319629585812073</v>
       </c>
       <c r="Q22">
-        <v>3.186385531067545E-15</v>
+        <v>0.9898037158156341</v>
       </c>
       <c r="R22">
-        <v>0.0009577089311353827</v>
+        <v>-120.9319629585812</v>
       </c>
       <c r="S22">
-        <v>0.0009577089311353827</v>
+        <v>0.9898037158156339</v>
       </c>
       <c r="T22">
-        <v>0.0009577089311353827</v>
+        <v>119.0680370414188</v>
       </c>
       <c r="U22">
-        <v>4.336808689942018E-19</v>
+        <v>0.9847697563539631</v>
       </c>
       <c r="V22">
-        <v>1.626278418073297E-30</v>
+        <v>-1.404484388589012</v>
       </c>
       <c r="W22">
-        <v>4.336808689942018E-19</v>
+        <v>0.9847697563539631</v>
+      </c>
+      <c r="X22">
+        <v>-121.404484388589</v>
+      </c>
+      <c r="Y22">
+        <v>0.9847697563539631</v>
+      </c>
+      <c r="Z22">
+        <v>118.595515611411</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/test_output.xlsx
+++ b/src/output/test_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>t</t>
   </si>
@@ -46,6 +46,51 @@
     <t>ct:CT3:Ic_ka</t>
   </si>
   <si>
+    <t>ct:CT4:Ia_ka</t>
+  </si>
+  <si>
+    <t>ct:CT4:Ib_ka</t>
+  </si>
+  <si>
+    <t>ct:CT4:Ic_ka</t>
+  </si>
+  <si>
+    <t>ct:CT5:Ia_ka</t>
+  </si>
+  <si>
+    <t>ct:CT5:Ib_ka</t>
+  </si>
+  <si>
+    <t>ct:CT5:Ic_ka</t>
+  </si>
+  <si>
+    <t>ct:CT6:Ia_ka</t>
+  </si>
+  <si>
+    <t>ct:CT6:Ib_ka</t>
+  </si>
+  <si>
+    <t>ct:CT6:Ic_ka</t>
+  </si>
+  <si>
+    <t>ct:CT7:Ia_ka</t>
+  </si>
+  <si>
+    <t>ct:CT7:Ib_ka</t>
+  </si>
+  <si>
+    <t>ct:CT7:Ic_ka</t>
+  </si>
+  <si>
+    <t>ct:CT8:Ia_ka</t>
+  </si>
+  <si>
+    <t>ct:CT8:Ib_ka</t>
+  </si>
+  <si>
+    <t>ct:CT8:Ic_ka</t>
+  </si>
+  <si>
     <t>cb:CB1:closed</t>
   </si>
   <si>
@@ -53,6 +98,21 @@
   </si>
   <si>
     <t>cb:CB3:closed</t>
+  </si>
+  <si>
+    <t>cb:CB4:closed</t>
+  </si>
+  <si>
+    <t>cb:CB5:closed</t>
+  </si>
+  <si>
+    <t>cb:CB6:closed</t>
+  </si>
+  <si>
+    <t>cb:CB7:closed</t>
+  </si>
+  <si>
+    <t>cb:CB8:closed</t>
   </si>
   <si>
     <t>bus:bus1:vm_a_pu</t>
@@ -464,10 +524,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:52">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,8 +621,68 @@
       <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:52">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -570,97 +690,157 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2563747790583773</v>
+        <v>0.3299778733226479</v>
       </c>
       <c r="D2">
-        <v>0.2563747790583774</v>
+        <v>0.3299778733226478</v>
       </c>
       <c r="E2">
-        <v>0.2563747790583774</v>
+        <v>0.3299778733226479</v>
       </c>
       <c r="F2">
-        <v>0.1468278212908316</v>
+        <v>0.1099926244450582</v>
       </c>
       <c r="G2">
-        <v>0.1468278212908316</v>
+        <v>0.1099926244450582</v>
       </c>
       <c r="H2">
-        <v>0.1468278212908316</v>
+        <v>0.1099926244450582</v>
       </c>
       <c r="I2">
-        <v>0.10955764975293</v>
+        <v>0.1099926244450582</v>
       </c>
       <c r="J2">
-        <v>0.1095576497529301</v>
+        <v>0.1099926244450582</v>
       </c>
       <c r="K2">
-        <v>0.1095576497529301</v>
-      </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
+        <v>0.1099926244450582</v>
+      </c>
+      <c r="L2">
+        <v>0.1099926244450582</v>
+      </c>
+      <c r="M2">
+        <v>0.1099926244450582</v>
+      </c>
+      <c r="N2">
+        <v>0.1099926244450582</v>
       </c>
       <c r="O2">
-        <v>0.9858504635033544</v>
+        <v>0.3299778733226504</v>
       </c>
       <c r="P2">
-        <v>-1.31339081535261</v>
+        <v>0.3299778733226504</v>
       </c>
       <c r="Q2">
-        <v>0.9858504635033543</v>
+        <v>0.3299778733226503</v>
       </c>
       <c r="R2">
-        <v>-121.3133908153526</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="S2">
-        <v>0.9858504635033543</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="T2">
-        <v>118.6866091846474</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="U2">
-        <v>0.9818187245813159</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="V2">
-        <v>-1.694105032947812</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="W2">
-        <v>0.9818187245813159</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="X2">
-        <v>-121.6941050329478</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="Y2">
-        <v>0.9818187245813159</v>
+        <v>0.1099926244450574</v>
       </c>
       <c r="Z2">
-        <v>118.3058949670522</v>
-      </c>
-      <c r="AA2">
-        <v>0.9829257148501604</v>
-      </c>
-      <c r="AB2">
-        <v>-1.600287068058186</v>
-      </c>
-      <c r="AC2">
-        <v>0.9829257148501601</v>
-      </c>
-      <c r="AD2">
-        <v>-121.6002870680582</v>
-      </c>
-      <c r="AE2">
-        <v>0.9829257148501603</v>
-      </c>
-      <c r="AF2">
-        <v>118.3997129319418</v>
+        <v>0.1099926244450574</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>0.9819825805158066</v>
+      </c>
+      <c r="AJ2">
+        <v>-1.701004507625294</v>
+      </c>
+      <c r="AK2">
+        <v>0.9819825805158064</v>
+      </c>
+      <c r="AL2">
+        <v>-121.7010045076253</v>
+      </c>
+      <c r="AM2">
+        <v>0.9819825805158063</v>
+      </c>
+      <c r="AN2">
+        <v>118.2989954923747</v>
+      </c>
+      <c r="AO2">
+        <v>0.9790460510627952</v>
+      </c>
+      <c r="AP2">
+        <v>-1.99017047214636</v>
+      </c>
+      <c r="AQ2">
+        <v>0.9790460510627951</v>
+      </c>
+      <c r="AR2">
+        <v>-121.9901704721463</v>
+      </c>
+      <c r="AS2">
+        <v>0.979046051062795</v>
+      </c>
+      <c r="AT2">
+        <v>118.0098295278536</v>
+      </c>
+      <c r="AU2">
+        <v>0.9790460510627952</v>
+      </c>
+      <c r="AV2">
+        <v>-1.99017047214636</v>
+      </c>
+      <c r="AW2">
+        <v>0.9790460510627951</v>
+      </c>
+      <c r="AX2">
+        <v>-121.9901704721463</v>
+      </c>
+      <c r="AY2">
+        <v>0.979046051062795</v>
+      </c>
+      <c r="AZ2">
+        <v>118.0098295278536</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:52">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -668,97 +848,157 @@
         <v>0.1</v>
       </c>
       <c r="C3">
-        <v>0.25979779585199</v>
+        <v>0.3344006249919294</v>
       </c>
       <c r="D3">
-        <v>0.2597977958519899</v>
+        <v>0.3344006249919294</v>
       </c>
       <c r="E3">
-        <v>0.2597977958519899</v>
+        <v>0.3344006249919294</v>
       </c>
       <c r="F3">
-        <v>0.1487890385458966</v>
+        <v>0.1114668750016158</v>
       </c>
       <c r="G3">
-        <v>0.1487890385458966</v>
+        <v>0.1114668750016158</v>
       </c>
       <c r="H3">
-        <v>0.1487890385458966</v>
+        <v>0.1114668750016158</v>
       </c>
       <c r="I3">
-        <v>0.111019601312908</v>
+        <v>0.1114668750016158</v>
       </c>
       <c r="J3">
-        <v>0.111019601312908</v>
+        <v>0.1114668750016158</v>
       </c>
       <c r="K3">
-        <v>0.111019601312908</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
+        <v>0.1114668750016158</v>
+      </c>
+      <c r="L3">
+        <v>0.1114668750016151</v>
+      </c>
+      <c r="M3">
+        <v>0.1114668750016151</v>
+      </c>
+      <c r="N3">
+        <v>0.1114668750016151</v>
       </c>
       <c r="O3">
-        <v>0.9856544178719623</v>
+        <v>0.3344006249919279</v>
       </c>
       <c r="P3">
-        <v>-1.330814389002745</v>
+        <v>0.3344006249919279</v>
       </c>
       <c r="Q3">
-        <v>0.9856544178719624</v>
+        <v>0.3344006249919279</v>
       </c>
       <c r="R3">
-        <v>-121.3308143890027</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="S3">
-        <v>0.9856544178719624</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="T3">
-        <v>118.6691856109972</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="U3">
-        <v>0.9815684101370595</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="V3">
-        <v>-1.716683818452057</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="W3">
-        <v>0.9815684101370594</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="X3">
-        <v>-121.7166838184521</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="Y3">
-        <v>0.9815684101370595</v>
+        <v>0.1114668750016159</v>
       </c>
       <c r="Z3">
-        <v>118.2833161815479</v>
-      </c>
-      <c r="AA3">
-        <v>0.9826903505787675</v>
-      </c>
-      <c r="AB3">
-        <v>-1.621590223844264</v>
-      </c>
-      <c r="AC3">
-        <v>0.9826903505787675</v>
-      </c>
-      <c r="AD3">
-        <v>-121.6215902238443</v>
-      </c>
-      <c r="AE3">
-        <v>0.9826903505787674</v>
-      </c>
-      <c r="AF3">
-        <v>118.3784097761557</v>
+        <v>0.1114668750016159</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <v>0.9817307776330906</v>
+      </c>
+      <c r="AJ3">
+        <v>-1.723670674638785</v>
+      </c>
+      <c r="AK3">
+        <v>0.9817307776330905</v>
+      </c>
+      <c r="AL3">
+        <v>-121.7236706746388</v>
+      </c>
+      <c r="AM3">
+        <v>0.9817307776330905</v>
+      </c>
+      <c r="AN3">
+        <v>118.2763293253612</v>
+      </c>
+      <c r="AO3">
+        <v>0.9787545948762605</v>
+      </c>
+      <c r="AP3">
+        <v>-2.016780862668933</v>
+      </c>
+      <c r="AQ3">
+        <v>0.9787545948762606</v>
+      </c>
+      <c r="AR3">
+        <v>-122.0167808626689</v>
+      </c>
+      <c r="AS3">
+        <v>0.9787545948762604</v>
+      </c>
+      <c r="AT3">
+        <v>117.983219137331</v>
+      </c>
+      <c r="AU3">
+        <v>0.9787545948762605</v>
+      </c>
+      <c r="AV3">
+        <v>-2.016780862668933</v>
+      </c>
+      <c r="AW3">
+        <v>0.9787545948762606</v>
+      </c>
+      <c r="AX3">
+        <v>-122.0167808626689</v>
+      </c>
+      <c r="AY3">
+        <v>0.9787545948762604</v>
+      </c>
+      <c r="AZ3">
+        <v>117.983219137331</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:52">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -766,97 +1006,157 @@
         <v>0.2</v>
       </c>
       <c r="C4">
-        <v>0.2632202394418394</v>
+        <v>0.3388231168325445</v>
       </c>
       <c r="D4">
-        <v>0.2632202394418394</v>
+        <v>0.3388231168325447</v>
       </c>
       <c r="E4">
-        <v>0.2632202394418394</v>
+        <v>0.3388231168325447</v>
       </c>
       <c r="F4">
-        <v>0.1507499544905336</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="G4">
-        <v>0.1507499544905336</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="H4">
-        <v>0.1507499544905336</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="I4">
-        <v>0.1124812816602687</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="J4">
-        <v>0.1124812816602686</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="K4">
-        <v>0.1124812816602687</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
+        <v>0.1129410389486222</v>
+      </c>
+      <c r="L4">
+        <v>0.1129410389486215</v>
+      </c>
+      <c r="M4">
+        <v>0.1129410389486215</v>
+      </c>
+      <c r="N4">
+        <v>0.1129410389486215</v>
       </c>
       <c r="O4">
-        <v>0.9854582635053271</v>
+        <v>0.3388231168325445</v>
       </c>
       <c r="P4">
-        <v>-1.348233401331072</v>
+        <v>0.3388231168325446</v>
       </c>
       <c r="Q4">
-        <v>0.9854582635053269</v>
+        <v>0.3388231168325447</v>
       </c>
       <c r="R4">
-        <v>-121.3482334013311</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="S4">
-        <v>0.9854582635053269</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="T4">
-        <v>118.6517665986689</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="U4">
-        <v>0.981317987316619</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="V4">
-        <v>-1.739259358777854</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="W4">
-        <v>0.9813179873166189</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="X4">
-        <v>-121.7392593587778</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="Y4">
-        <v>0.9813179873166187</v>
+        <v>0.1129410389486222</v>
       </c>
       <c r="Z4">
-        <v>118.2607406412221</v>
-      </c>
-      <c r="AA4">
-        <v>0.9824548803524933</v>
-      </c>
-      <c r="AB4">
-        <v>-1.642889685515492</v>
-      </c>
-      <c r="AC4">
-        <v>0.9824548803524933</v>
-      </c>
-      <c r="AD4">
-        <v>-121.6428896855155</v>
-      </c>
-      <c r="AE4">
-        <v>0.9824548803524932</v>
-      </c>
-      <c r="AF4">
-        <v>118.3571103144845</v>
+        <v>0.1129410389486222</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <v>0.9814787784004816</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.746333849923062</v>
+      </c>
+      <c r="AK4">
+        <v>0.9814787784004815</v>
+      </c>
+      <c r="AL4">
+        <v>-121.7463338499231</v>
+      </c>
+      <c r="AM4">
+        <v>0.9814787784004815</v>
+      </c>
+      <c r="AN4">
+        <v>118.2536661500769</v>
+      </c>
+      <c r="AO4">
+        <v>0.9784629400194321</v>
+      </c>
+      <c r="AP4">
+        <v>-2.043390117674582</v>
+      </c>
+      <c r="AQ4">
+        <v>0.978462940019432</v>
+      </c>
+      <c r="AR4">
+        <v>-122.0433901176746</v>
+      </c>
+      <c r="AS4">
+        <v>0.9784629400194319</v>
+      </c>
+      <c r="AT4">
+        <v>117.9566098823254</v>
+      </c>
+      <c r="AU4">
+        <v>0.9784629400194321</v>
+      </c>
+      <c r="AV4">
+        <v>-2.043390117674582</v>
+      </c>
+      <c r="AW4">
+        <v>0.978462940019432</v>
+      </c>
+      <c r="AX4">
+        <v>-122.0433901176746</v>
+      </c>
+      <c r="AY4">
+        <v>0.9784629400194319</v>
+      </c>
+      <c r="AZ4">
+        <v>117.9566098823254</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:52">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -864,97 +1164,157 @@
         <v>0.3</v>
       </c>
       <c r="C5">
-        <v>0.2666397630972633</v>
+        <v>0.3432423175031984</v>
       </c>
       <c r="D5">
-        <v>0.2666397630972634</v>
+        <v>0.3432423175031984</v>
       </c>
       <c r="E5">
-        <v>0.2666397630972634</v>
+        <v>0.3432423175031984</v>
       </c>
       <c r="F5">
-        <v>0.1527092245431256</v>
+        <v>0.1144141058389818</v>
       </c>
       <c r="G5">
-        <v>0.1527092245431256</v>
+        <v>0.1144141058389818</v>
       </c>
       <c r="H5">
-        <v>0.1527092245431256</v>
+        <v>0.1144141058389818</v>
       </c>
       <c r="I5">
-        <v>0.1139416885414792</v>
+        <v>0.1144141058389818</v>
       </c>
       <c r="J5">
-        <v>0.1139416885414792</v>
+        <v>0.1144141058389818</v>
       </c>
       <c r="K5">
-        <v>0.1139416885414792</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
+        <v>0.1144141058389818</v>
+      </c>
+      <c r="L5">
+        <v>0.1144141058389818</v>
+      </c>
+      <c r="M5">
+        <v>0.1144141058389818</v>
+      </c>
+      <c r="N5">
+        <v>0.1144141058389818</v>
       </c>
       <c r="O5">
-        <v>0.9852621351183863</v>
+        <v>0.3432423175032002</v>
       </c>
       <c r="P5">
-        <v>-1.365635911053661</v>
+        <v>0.3432423175032003</v>
       </c>
       <c r="Q5">
-        <v>0.9852621351183865</v>
+        <v>0.3432423175032003</v>
       </c>
       <c r="R5">
-        <v>-121.3656359110537</v>
+        <v>0.1144141058389796</v>
       </c>
       <c r="S5">
-        <v>0.9852621351183862</v>
+        <v>0.1144141058389796</v>
       </c>
       <c r="T5">
-        <v>118.6343640889463</v>
+        <v>0.1144141058389797</v>
       </c>
       <c r="U5">
-        <v>0.9810676280528884</v>
+        <v>0.1144141058389796</v>
       </c>
       <c r="V5">
-        <v>-1.761816177219299</v>
+        <v>0.1144141058389796</v>
       </c>
       <c r="W5">
-        <v>0.9810676280528884</v>
+        <v>0.1144141058389797</v>
       </c>
       <c r="X5">
-        <v>-121.7618161772193</v>
+        <v>0.1144141058389796</v>
       </c>
       <c r="Y5">
-        <v>0.9810676280528884</v>
+        <v>0.1144141058389796</v>
       </c>
       <c r="Z5">
-        <v>118.2381838227807</v>
-      </c>
-      <c r="AA5">
-        <v>0.9822194658485601</v>
-      </c>
-      <c r="AB5">
-        <v>-1.664170851219349</v>
-      </c>
-      <c r="AC5">
-        <v>0.9822194658485599</v>
-      </c>
-      <c r="AD5">
-        <v>-121.6641708512194</v>
-      </c>
-      <c r="AE5">
-        <v>0.9822194658485599</v>
-      </c>
-      <c r="AF5">
-        <v>118.3358291487806</v>
+        <v>0.1144141058389797</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>0.9812267557930013</v>
+      </c>
+      <c r="AJ5">
+        <v>-1.768978503072318</v>
+      </c>
+      <c r="AK5">
+        <v>0.9812267557930012</v>
+      </c>
+      <c r="AL5">
+        <v>-121.7689785030723</v>
+      </c>
+      <c r="AM5">
+        <v>0.9812267557930012</v>
+      </c>
+      <c r="AN5">
+        <v>118.2310214969277</v>
+      </c>
+      <c r="AO5">
+        <v>0.9781712866502154</v>
+      </c>
+      <c r="AP5">
+        <v>-2.06998000366035</v>
+      </c>
+      <c r="AQ5">
+        <v>0.9781712866502154</v>
+      </c>
+      <c r="AR5">
+        <v>-122.0699800036603</v>
+      </c>
+      <c r="AS5">
+        <v>0.9781712866502152</v>
+      </c>
+      <c r="AT5">
+        <v>117.9300199963396</v>
+      </c>
+      <c r="AU5">
+        <v>0.9781712866502154</v>
+      </c>
+      <c r="AV5">
+        <v>-2.06998000366035</v>
+      </c>
+      <c r="AW5">
+        <v>0.9781712866502154</v>
+      </c>
+      <c r="AX5">
+        <v>-122.0699800036603</v>
+      </c>
+      <c r="AY5">
+        <v>0.9781712866502152</v>
+      </c>
+      <c r="AZ5">
+        <v>117.9300199963396</v>
       </c>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:52">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -962,97 +1322,157 @@
         <v>0.4</v>
       </c>
       <c r="C6">
-        <v>0.2700540184330826</v>
+        <v>0.347655192200187</v>
       </c>
       <c r="D6">
-        <v>0.2700540184330825</v>
+        <v>0.347655192200187</v>
       </c>
       <c r="E6">
-        <v>0.2700540184330826</v>
+        <v>0.3476551922001871</v>
       </c>
       <c r="F6">
-        <v>0.154665503099462</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="G6">
-        <v>0.1546655030994619</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="H6">
-        <v>0.154665503099462</v>
+        <v>0.1158850640714417</v>
       </c>
       <c r="I6">
-        <v>0.1153998190691314</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="J6">
-        <v>0.1153998190691313</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="K6">
-        <v>0.1153998190691313</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" t="b">
-        <v>1</v>
+        <v>0.1158850640714416</v>
+      </c>
+      <c r="L6">
+        <v>0.1158850640714416</v>
+      </c>
+      <c r="M6">
+        <v>0.1158850640714416</v>
+      </c>
+      <c r="N6">
+        <v>0.1158850640714417</v>
       </c>
       <c r="O6">
-        <v>0.9850661679088053</v>
+        <v>0.347655192200187</v>
       </c>
       <c r="P6">
-        <v>-1.383009972957798</v>
+        <v>0.347655192200187</v>
       </c>
       <c r="Q6">
-        <v>0.9850661679088051</v>
+        <v>0.3476551922001871</v>
       </c>
       <c r="R6">
-        <v>-121.3830099729578</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="S6">
-        <v>0.9850661679088051</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="T6">
-        <v>118.6169900270422</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="U6">
-        <v>0.9808175048116948</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="V6">
-        <v>-1.784338784651976</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="W6">
-        <v>0.9808175048116947</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="X6">
-        <v>-121.784338784652</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="Y6">
-        <v>0.9808175048116945</v>
+        <v>0.1158850640714416</v>
       </c>
       <c r="Z6">
-        <v>118.215661215348</v>
-      </c>
-      <c r="AA6">
-        <v>0.9819842692563671</v>
-      </c>
-      <c r="AB6">
-        <v>-1.68541910912456</v>
-      </c>
-      <c r="AC6">
-        <v>0.9819842692563669</v>
-      </c>
-      <c r="AD6">
-        <v>-121.6854191091246</v>
-      </c>
-      <c r="AE6">
-        <v>0.9819842692563669</v>
-      </c>
-      <c r="AF6">
-        <v>118.3145808908754</v>
+        <v>0.1158850640714416</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>0.9809748835616305</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.791589090457418</v>
+      </c>
+      <c r="AK6">
+        <v>0.9809748835616307</v>
+      </c>
+      <c r="AL6">
+        <v>-121.7915890904574</v>
+      </c>
+      <c r="AM6">
+        <v>0.9809748835616305</v>
+      </c>
+      <c r="AN6">
+        <v>118.2084109095426</v>
+      </c>
+      <c r="AO6">
+        <v>0.9778798357463073</v>
+      </c>
+      <c r="AP6">
+        <v>-2.096532265063697</v>
+      </c>
+      <c r="AQ6">
+        <v>0.9778798357463074</v>
+      </c>
+      <c r="AR6">
+        <v>-122.0965322650637</v>
+      </c>
+      <c r="AS6">
+        <v>0.9778798357463072</v>
+      </c>
+      <c r="AT6">
+        <v>117.9034677349363</v>
+      </c>
+      <c r="AU6">
+        <v>0.9778798357463073</v>
+      </c>
+      <c r="AV6">
+        <v>-2.096532265063697</v>
+      </c>
+      <c r="AW6">
+        <v>0.9778798357463074</v>
+      </c>
+      <c r="AX6">
+        <v>-122.0965322650637</v>
+      </c>
+      <c r="AY6">
+        <v>0.9778798357463072</v>
+      </c>
+      <c r="AZ6">
+        <v>117.9034677349363</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:52">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1060,97 +1480,157 @@
         <v>0.5</v>
       </c>
       <c r="C7">
-        <v>0.2734606570174363</v>
+        <v>0.3520587047257959</v>
       </c>
       <c r="D7">
-        <v>0.2734606570174363</v>
+        <v>0.352058704725796</v>
       </c>
       <c r="E7">
-        <v>0.2734606570174363</v>
+        <v>0.352058704725796</v>
       </c>
       <c r="F7">
-        <v>0.1566174444538758</v>
+        <v>0.1173529015801155</v>
       </c>
       <c r="G7">
-        <v>0.1566174444538758</v>
+        <v>0.1173529015801155</v>
       </c>
       <c r="H7">
-        <v>0.1566174444538758</v>
+        <v>0.1173529015801156</v>
       </c>
       <c r="I7">
-        <v>0.1168546704086218</v>
+        <v>0.1173529015801155</v>
       </c>
       <c r="J7">
-        <v>0.1168546704086219</v>
+        <v>0.1173529015801155</v>
       </c>
       <c r="K7">
-        <v>0.1168546704086218</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
+        <v>0.1173529015801156</v>
+      </c>
+      <c r="L7">
+        <v>0.1173529015801155</v>
+      </c>
+      <c r="M7">
+        <v>0.1173529015801155</v>
+      </c>
+      <c r="N7">
+        <v>0.1173529015801155</v>
       </c>
       <c r="O7">
-        <v>0.984870497463776</v>
+        <v>0.3520587047257944</v>
       </c>
       <c r="P7">
-        <v>-1.400343646071891</v>
+        <v>0.3520587047257943</v>
       </c>
       <c r="Q7">
-        <v>0.9848704974637761</v>
+        <v>0.3520587047257943</v>
       </c>
       <c r="R7">
-        <v>-121.4003436460719</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="S7">
-        <v>0.9848704974637759</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="T7">
-        <v>118.5996563539281</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="U7">
-        <v>0.980567790473085</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="V7">
-        <v>-1.806811690116421</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="W7">
-        <v>0.9805677904730851</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="X7">
-        <v>-121.8068116901164</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="Y7">
-        <v>0.980567790473085</v>
+        <v>0.1173529015801177</v>
       </c>
       <c r="Z7">
-        <v>118.1931883098836</v>
-      </c>
-      <c r="AA7">
-        <v>0.9817494531658117</v>
-      </c>
-      <c r="AB7">
-        <v>-1.706619847408013</v>
-      </c>
-      <c r="AC7">
-        <v>0.9817494531658119</v>
-      </c>
-      <c r="AD7">
-        <v>-121.706619847408</v>
-      </c>
-      <c r="AE7">
-        <v>0.9817494531658119</v>
-      </c>
-      <c r="AF7">
-        <v>118.293380152592</v>
+        <v>0.1173529015801177</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>0.9807233361144213</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.81415006580597</v>
+      </c>
+      <c r="AK7">
+        <v>0.9807233361144215</v>
+      </c>
+      <c r="AL7">
+        <v>-121.814150065806</v>
+      </c>
+      <c r="AM7">
+        <v>0.9807233361144213</v>
+      </c>
+      <c r="AN7">
+        <v>118.185849934194</v>
+      </c>
+      <c r="AO7">
+        <v>0.9775887889677535</v>
+      </c>
+      <c r="AP7">
+        <v>-2.123028636670325</v>
+      </c>
+      <c r="AQ7">
+        <v>0.9775887889677534</v>
+      </c>
+      <c r="AR7">
+        <v>-122.1230286366703</v>
+      </c>
+      <c r="AS7">
+        <v>0.9775887889677533</v>
+      </c>
+      <c r="AT7">
+        <v>117.8769713633297</v>
+      </c>
+      <c r="AU7">
+        <v>0.9775887889677535</v>
+      </c>
+      <c r="AV7">
+        <v>-2.123028636670324</v>
+      </c>
+      <c r="AW7">
+        <v>0.9775887889677534</v>
+      </c>
+      <c r="AX7">
+        <v>-122.1230286366703</v>
+      </c>
+      <c r="AY7">
+        <v>0.9775887889677533</v>
+      </c>
+      <c r="AZ7">
+        <v>117.8769713633297</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:52">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1158,97 +1638,157 @@
         <v>0.6</v>
       </c>
       <c r="C8">
-        <v>0.3989351224990861</v>
+        <v>0.4486251819410546</v>
       </c>
       <c r="D8">
-        <v>0.398935122499086</v>
+        <v>0.4486251819410547</v>
       </c>
       <c r="E8">
-        <v>0.3989351224990861</v>
+        <v>0.4486251819410547</v>
       </c>
       <c r="F8">
-        <v>0.1597145613713661</v>
+        <v>0.1194727067493352</v>
       </c>
       <c r="G8">
-        <v>0.1597145613713661</v>
+        <v>0.1194727067493352</v>
       </c>
       <c r="H8">
-        <v>0.1597145613713661</v>
+        <v>0.1194727067493352</v>
       </c>
       <c r="I8">
-        <v>0.2392264415837599</v>
+        <v>0.2096816460853277</v>
       </c>
       <c r="J8">
-        <v>0.2392264415837599</v>
+        <v>0.2096816460853276</v>
       </c>
       <c r="K8">
-        <v>0.2392264415837599</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
+        <v>0.2096816460853277</v>
+      </c>
+      <c r="L8">
+        <v>0.1194727067493352</v>
+      </c>
+      <c r="M8">
+        <v>0.1194727067493352</v>
+      </c>
+      <c r="N8">
+        <v>0.1194727067493352</v>
       </c>
       <c r="O8">
-        <v>0.9776533835426393</v>
+        <v>0.3564498195736564</v>
       </c>
       <c r="P8">
-        <v>-2.040798778922309</v>
+        <v>0.3564498195736566</v>
       </c>
       <c r="Q8">
-        <v>0.9776533835426393</v>
+        <v>0.3564498195736566</v>
       </c>
       <c r="R8">
-        <v>-122.0407987789223</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="S8">
-        <v>0.9776533835426391</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="T8">
-        <v>117.9592012210777</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="U8">
-        <v>0.9732646672060854</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="V8">
-        <v>-2.458350956046335</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="W8">
-        <v>0.9732646672060853</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="X8">
-        <v>-122.4583509560463</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="Y8">
-        <v>0.9732646672060852</v>
+        <v>0.118816606529543</v>
       </c>
       <c r="Z8">
-        <v>117.5416490439537</v>
-      </c>
-      <c r="AA8">
-        <v>0.9712240116537364</v>
-      </c>
-      <c r="AB8">
-        <v>-2.671926257162932</v>
-      </c>
-      <c r="AC8">
-        <v>0.9712240116537363</v>
-      </c>
-      <c r="AD8">
-        <v>-122.6719262571629</v>
-      </c>
-      <c r="AE8">
-        <v>0.9712240116537361</v>
-      </c>
-      <c r="AF8">
-        <v>117.3280737428371</v>
+        <v>0.118816606529543</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>0.9751324657252497</v>
+      </c>
+      <c r="AJ8">
+        <v>-2.307718981458547</v>
+      </c>
+      <c r="AK8">
+        <v>0.9751324657252496</v>
+      </c>
+      <c r="AL8">
+        <v>-122.3077189814585</v>
+      </c>
+      <c r="AM8">
+        <v>0.9751324657252495</v>
+      </c>
+      <c r="AN8">
+        <v>117.6922810185414</v>
+      </c>
+      <c r="AO8">
+        <v>0.9719407402675391</v>
+      </c>
+      <c r="AP8">
+        <v>-2.623968230808478</v>
+      </c>
+      <c r="AQ8">
+        <v>0.9719407402675392</v>
+      </c>
+      <c r="AR8">
+        <v>-122.6239682308085</v>
+      </c>
+      <c r="AS8">
+        <v>0.9719407402675388</v>
+      </c>
+      <c r="AT8">
+        <v>117.3760317691915</v>
+      </c>
+      <c r="AU8">
+        <v>0.9695044945680414</v>
+      </c>
+      <c r="AV8">
+        <v>-2.862388775331294</v>
+      </c>
+      <c r="AW8">
+        <v>0.9695044945680413</v>
+      </c>
+      <c r="AX8">
+        <v>-122.8623887753313</v>
+      </c>
+      <c r="AY8">
+        <v>0.9695044945680412</v>
+      </c>
+      <c r="AZ8">
+        <v>117.1376112246687</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:52">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1256,22 +1796,22 @@
         <v>0.7</v>
       </c>
       <c r="C9">
-        <v>0.15941001414414</v>
+        <v>0.2388740982730588</v>
       </c>
       <c r="D9">
-        <v>0.15941001414414</v>
+        <v>0.2388740982730588</v>
       </c>
       <c r="E9">
-        <v>0.15941001414414</v>
+        <v>0.2388740982730588</v>
       </c>
       <c r="F9">
-        <v>0.1594100141474568</v>
+        <v>0.11943704913949</v>
       </c>
       <c r="G9">
-        <v>0.1594100141474568</v>
+        <v>0.11943704913949</v>
       </c>
       <c r="H9">
-        <v>0.1594100141474567</v>
+        <v>0.11943704913949</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1282,71 +1822,131 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
+      <c r="L9">
+        <v>0.11943704913949</v>
+      </c>
+      <c r="M9">
+        <v>0.11943704913949</v>
+      </c>
+      <c r="N9">
+        <v>0.11943704913949</v>
       </c>
       <c r="O9">
-        <v>0.991160002998693</v>
+        <v>0.3608255040294972</v>
       </c>
       <c r="P9">
-        <v>-0.8126050944476874</v>
+        <v>0.3608255040294971</v>
       </c>
       <c r="Q9">
-        <v>0.9911600029986931</v>
+        <v>0.3608255040294972</v>
       </c>
       <c r="R9">
-        <v>-120.8126050944477</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="S9">
-        <v>0.991160002998693</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="T9">
-        <v>119.1873949055523</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="U9">
-        <v>0.9867801912369689</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="V9">
-        <v>-1.223689689051793</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="W9">
-        <v>0.9867801912369688</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="X9">
-        <v>-121.2236896890518</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="Y9">
-        <v>0.986780191236969</v>
+        <v>0.120275168014956</v>
       </c>
       <c r="Z9">
-        <v>118.7763103109482</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
+        <v>0.120275168014956</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>0.987043078809302</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.231003427455619</v>
+      </c>
+      <c r="AK9">
+        <v>0.987043078809302</v>
+      </c>
+      <c r="AL9">
+        <v>-121.2310034274556</v>
+      </c>
+      <c r="AM9">
+        <v>0.9870430788093019</v>
+      </c>
+      <c r="AN9">
+        <v>118.7689965725444</v>
+      </c>
+      <c r="AO9">
+        <v>0.9838525997946462</v>
+      </c>
+      <c r="AP9">
+        <v>-1.543349301469048</v>
+      </c>
+      <c r="AQ9">
+        <v>0.9838525997946462</v>
+      </c>
+      <c r="AR9">
+        <v>-121.543349301469</v>
+      </c>
+      <c r="AS9">
+        <v>0.9838525997946461</v>
+      </c>
+      <c r="AT9">
+        <v>118.456650698531</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:52">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1354,22 +1954,22 @@
         <v>0.8</v>
       </c>
       <c r="C10">
-        <v>0.1613134456442891</v>
+        <v>0.2417362808119734</v>
       </c>
       <c r="D10">
-        <v>0.1613134456442892</v>
+        <v>0.2417362808119734</v>
       </c>
       <c r="E10">
-        <v>0.1613134456442892</v>
+        <v>0.2417362808119734</v>
       </c>
       <c r="F10">
-        <v>0.1613134456477266</v>
+        <v>0.1208681404090558</v>
       </c>
       <c r="G10">
-        <v>0.1613134456477267</v>
+        <v>0.1208681404090557</v>
       </c>
       <c r="H10">
-        <v>0.1613134456477266</v>
+        <v>0.1208681404090558</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1380,71 +1980,131 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" t="b">
-        <v>0</v>
+      <c r="L10">
+        <v>0.1208681404090558</v>
+      </c>
+      <c r="M10">
+        <v>0.1208681404090557</v>
+      </c>
+      <c r="N10">
+        <v>0.1208681404090558</v>
       </c>
       <c r="O10">
-        <v>0.9910509503245907</v>
+        <v>0.3651827302862463</v>
       </c>
       <c r="P10">
-        <v>-0.822236793493437</v>
+        <v>0.3651827302862464</v>
       </c>
       <c r="Q10">
-        <v>0.9910509503245909</v>
+        <v>0.3651827302862465</v>
       </c>
       <c r="R10">
-        <v>-120.8222367934934</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="S10">
-        <v>0.9910509503245908</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="T10">
-        <v>119.1777632065065</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="U10">
-        <v>0.9866184260991979</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="V10">
-        <v>-1.238269659606543</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="W10">
-        <v>0.9866184260991979</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="X10">
-        <v>-121.2382696596065</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="Y10">
-        <v>0.9866184260991979</v>
+        <v>0.1217275767673436</v>
       </c>
       <c r="Z10">
-        <v>118.7617303403935</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
+        <v>0.1217275767673436</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>0.9868820520918218</v>
+      </c>
+      <c r="AJ10">
+        <v>-1.245661977244771</v>
+      </c>
+      <c r="AK10">
+        <v>0.9868820520918218</v>
+      </c>
+      <c r="AL10">
+        <v>-121.2456619772448</v>
+      </c>
+      <c r="AM10">
+        <v>0.9868820520918217</v>
+      </c>
+      <c r="AN10">
+        <v>118.7543380227552</v>
+      </c>
+      <c r="AO10">
+        <v>0.9836530562202728</v>
+      </c>
+      <c r="AP10">
+        <v>-1.561796009534571</v>
+      </c>
+      <c r="AQ10">
+        <v>0.9836530562202729</v>
+      </c>
+      <c r="AR10">
+        <v>-121.5617960095346</v>
+      </c>
+      <c r="AS10">
+        <v>0.9836530562202725</v>
+      </c>
+      <c r="AT10">
+        <v>118.4382039904654</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:52">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1452,22 +2112,22 @@
         <v>0.9</v>
       </c>
       <c r="C11">
-        <v>0.1632069527779923</v>
+        <v>0.2445837781612257</v>
       </c>
       <c r="D11">
-        <v>0.1632069527779923</v>
+        <v>0.2445837781612257</v>
       </c>
       <c r="E11">
-        <v>0.1632069527779922</v>
+        <v>0.2445837781612257</v>
       </c>
       <c r="F11">
-        <v>0.1632069527815576</v>
+        <v>0.1222918890837863</v>
       </c>
       <c r="G11">
-        <v>0.1632069527815576</v>
+        <v>0.1222918890837863</v>
       </c>
       <c r="H11">
-        <v>0.1632069527815575</v>
+        <v>0.1222918890837863</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1478,71 +2138,131 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
+      <c r="L11">
+        <v>0.1222918890837863</v>
+      </c>
+      <c r="M11">
+        <v>0.1222918890837863</v>
+      </c>
+      <c r="N11">
+        <v>0.1222918890837863</v>
       </c>
       <c r="O11">
-        <v>0.9909424093224313</v>
+        <v>0.3695184775718983</v>
       </c>
       <c r="P11">
-        <v>-0.831817244107633</v>
+        <v>0.3695184775718982</v>
       </c>
       <c r="Q11">
-        <v>0.9909424093224316</v>
+        <v>0.3695184775718983</v>
       </c>
       <c r="R11">
-        <v>-120.8318172441076</v>
+        <v>0.1231728258626953</v>
       </c>
       <c r="S11">
-        <v>0.9909424093224314</v>
+        <v>0.1231728258626953</v>
       </c>
       <c r="T11">
-        <v>119.1681827558924</v>
+        <v>0.1231728258626954</v>
       </c>
       <c r="U11">
-        <v>0.9864574401396828</v>
+        <v>0.1231728258626953</v>
       </c>
       <c r="V11">
-        <v>-1.252773689125451</v>
+        <v>0.1231728258626953</v>
       </c>
       <c r="W11">
-        <v>0.9864574401396827</v>
+        <v>0.1231728258626954</v>
       </c>
       <c r="X11">
-        <v>-121.2527736891254</v>
+        <v>0.1231728258626953</v>
       </c>
       <c r="Y11">
-        <v>0.9864574401396827</v>
+        <v>0.1231728258626953</v>
       </c>
       <c r="Z11">
-        <v>118.7472263108745</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
+        <v>0.1231728258626954</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>0.986721752965194</v>
+      </c>
+      <c r="AJ11">
+        <v>-1.260244214922184</v>
+      </c>
+      <c r="AK11">
+        <v>0.986721752965194</v>
+      </c>
+      <c r="AL11">
+        <v>-121.2602442149222</v>
+      </c>
+      <c r="AM11">
+        <v>0.9867217529651939</v>
+      </c>
+      <c r="AN11">
+        <v>118.7397557850778</v>
+      </c>
+      <c r="AO11">
+        <v>0.983454433579744</v>
+      </c>
+      <c r="AP11">
+        <v>-1.580148228874273</v>
+      </c>
+      <c r="AQ11">
+        <v>0.983454433579744</v>
+      </c>
+      <c r="AR11">
+        <v>-121.5801482288743</v>
+      </c>
+      <c r="AS11">
+        <v>0.983454433579744</v>
+      </c>
+      <c r="AT11">
+        <v>118.4198517711257</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:52">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1550,22 +2270,22 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.1650892275134926</v>
+        <v>0.2474146199264144</v>
       </c>
       <c r="D12">
-        <v>0.1650892275134926</v>
+        <v>0.2474146199264145</v>
       </c>
       <c r="E12">
-        <v>0.1650892275134926</v>
+        <v>0.2474146199264146</v>
       </c>
       <c r="F12">
-        <v>0.1650892275171981</v>
+        <v>0.1237073099664838</v>
       </c>
       <c r="G12">
-        <v>0.1650892275171981</v>
+        <v>0.1237073099664838</v>
       </c>
       <c r="H12">
-        <v>0.1650892275171981</v>
+        <v>0.1237073099664838</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1576,71 +2296,131 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
+      <c r="L12">
+        <v>0.1237073099664838</v>
+      </c>
+      <c r="M12">
+        <v>0.1237073099664838</v>
+      </c>
+      <c r="N12">
+        <v>0.1237073099664838</v>
       </c>
       <c r="O12">
-        <v>0.9908344559245704</v>
+        <v>0.3738297342888183</v>
       </c>
       <c r="P12">
-        <v>-0.8413398450527552</v>
+        <v>0.3738297342888184</v>
       </c>
       <c r="Q12">
-        <v>0.9908344559245704</v>
+        <v>0.3738297342888184</v>
       </c>
       <c r="R12">
-        <v>-120.8413398450527</v>
+        <v>0.1246099114351322</v>
       </c>
       <c r="S12">
-        <v>0.9908344559245704</v>
+        <v>0.1246099114351322</v>
       </c>
       <c r="T12">
-        <v>119.1586601549473</v>
+        <v>0.1246099114351323</v>
       </c>
       <c r="U12">
-        <v>0.9862973456395486</v>
+        <v>0.1246099114351322</v>
       </c>
       <c r="V12">
-        <v>-1.267191757914976</v>
+        <v>0.1246099114351322</v>
       </c>
       <c r="W12">
-        <v>0.9862973456395487</v>
+        <v>0.1246099114351323</v>
       </c>
       <c r="X12">
-        <v>-121.267191757915</v>
+        <v>0.1246099114351322</v>
       </c>
       <c r="Y12">
-        <v>0.9862973456395486</v>
+        <v>0.1246099114351322</v>
       </c>
       <c r="Z12">
-        <v>118.732808242085</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
+        <v>0.1246099114351323</v>
+      </c>
+      <c r="AA12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>0.9865622939741341</v>
+      </c>
+      <c r="AJ12">
+        <v>-1.274740068324712</v>
+      </c>
+      <c r="AK12">
+        <v>0.9865622939741342</v>
+      </c>
+      <c r="AL12">
+        <v>-121.2747400683247</v>
+      </c>
+      <c r="AM12">
+        <v>0.9865622939741341</v>
+      </c>
+      <c r="AN12">
+        <v>118.7252599316753</v>
+      </c>
+      <c r="AO12">
+        <v>0.9832568710046815</v>
+      </c>
+      <c r="AP12">
+        <v>-1.598393259622906</v>
+      </c>
+      <c r="AQ12">
+        <v>0.9832568710046816</v>
+      </c>
+      <c r="AR12">
+        <v>-121.5983932596229</v>
+      </c>
+      <c r="AS12">
+        <v>0.9832568710046816</v>
+      </c>
+      <c r="AT12">
+        <v>118.4016067403771</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:52">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1648,22 +2428,22 @@
         <v>1.1</v>
       </c>
       <c r="C13">
-        <v>0.166958968253512</v>
+        <v>0.2502268447402418</v>
       </c>
       <c r="D13">
-        <v>0.166958968253512</v>
+        <v>0.2502268447402418</v>
       </c>
       <c r="E13">
-        <v>0.166958968253512</v>
+        <v>0.2502268447402418</v>
       </c>
       <c r="F13">
-        <v>0.166958968257344</v>
+        <v>0.1251134223735034</v>
       </c>
       <c r="G13">
-        <v>0.166958968257344</v>
+        <v>0.1251134223735034</v>
       </c>
       <c r="H13">
-        <v>0.166958968257344</v>
+        <v>0.1251134223735035</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1674,71 +2454,131 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" t="b">
-        <v>0</v>
+      <c r="L13">
+        <v>0.1251134223735034</v>
+      </c>
+      <c r="M13">
+        <v>0.1251134223735034</v>
+      </c>
+      <c r="N13">
+        <v>0.1251134223735035</v>
       </c>
       <c r="O13">
-        <v>0.990727165844396</v>
+        <v>0.3781135001630304</v>
       </c>
       <c r="P13">
-        <v>-0.850798030366923</v>
+        <v>0.3781135001630304</v>
       </c>
       <c r="Q13">
-        <v>0.9907271658443959</v>
+        <v>0.3781135001630305</v>
       </c>
       <c r="R13">
-        <v>-120.8507980303669</v>
+        <v>0.1260378333933352</v>
       </c>
       <c r="S13">
-        <v>0.990727165844396</v>
+        <v>0.1260378333933352</v>
       </c>
       <c r="T13">
-        <v>119.1492019696331</v>
+        <v>0.1260378333933352</v>
       </c>
       <c r="U13">
-        <v>0.9861382545021613</v>
+        <v>0.1260378333933345</v>
       </c>
       <c r="V13">
-        <v>-1.281513895324309</v>
+        <v>0.1260378333933345</v>
       </c>
       <c r="W13">
-        <v>0.9861382545021611</v>
+        <v>0.1260378333933345</v>
       </c>
       <c r="X13">
-        <v>-121.2815138953243</v>
+        <v>0.1260378333933345</v>
       </c>
       <c r="Y13">
-        <v>0.9861382545021612</v>
+        <v>0.1260378333933345</v>
       </c>
       <c r="Z13">
-        <v>118.7184861046757</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
+        <v>0.1260378333933345</v>
+      </c>
+      <c r="AA13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI13">
+        <v>0.9864037874157465</v>
+      </c>
+      <c r="AJ13">
+        <v>-1.289139514416606</v>
+      </c>
+      <c r="AK13">
+        <v>0.9864037874157464</v>
+      </c>
+      <c r="AL13">
+        <v>-121.2891395144166</v>
+      </c>
+      <c r="AM13">
+        <v>0.9864037874157464</v>
+      </c>
+      <c r="AN13">
+        <v>118.7108604855834</v>
+      </c>
+      <c r="AO13">
+        <v>0.9830605072690023</v>
+      </c>
+      <c r="AP13">
+        <v>-1.616518459600611</v>
+      </c>
+      <c r="AQ13">
+        <v>0.9830605072690024</v>
+      </c>
+      <c r="AR13">
+        <v>-121.6165184596006</v>
+      </c>
+      <c r="AS13">
+        <v>0.9830605072690022</v>
+      </c>
+      <c r="AT13">
+        <v>118.3834815403994</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:52">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1746,22 +2586,22 @@
         <v>1.2</v>
       </c>
       <c r="C14">
-        <v>0.1688148807561272</v>
+        <v>0.2530185016579669</v>
       </c>
       <c r="D14">
-        <v>0.1688148807561272</v>
+        <v>0.253018501657967</v>
       </c>
       <c r="E14">
-        <v>0.1688148807561272</v>
+        <v>0.2530185016579669</v>
       </c>
       <c r="F14">
-        <v>0.1688148807600887</v>
+        <v>0.1265092508324734</v>
       </c>
       <c r="G14">
-        <v>0.1688148807600887</v>
+        <v>0.1265092508324735</v>
       </c>
       <c r="H14">
-        <v>0.1688148807600887</v>
+        <v>0.1265092508324735</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1772,71 +2612,131 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
+      <c r="L14">
+        <v>0.1265092508324734</v>
+      </c>
+      <c r="M14">
+        <v>0.1265092508324735</v>
+      </c>
+      <c r="N14">
+        <v>0.1265092508324735</v>
       </c>
       <c r="O14">
-        <v>0.9906206145200305</v>
+        <v>0.3823667884017996</v>
       </c>
       <c r="P14">
-        <v>-0.8601852739617384</v>
+        <v>0.3823667884017996</v>
       </c>
       <c r="Q14">
-        <v>0.9906206145200305</v>
+        <v>0.3823667884017996</v>
       </c>
       <c r="R14">
-        <v>-120.8601852739617</v>
+        <v>0.1274555961397252</v>
       </c>
       <c r="S14">
-        <v>0.9906206145200306</v>
+        <v>0.1274555961397252</v>
       </c>
       <c r="T14">
-        <v>119.1398147260382</v>
+        <v>0.1274555961397253</v>
       </c>
       <c r="U14">
-        <v>0.9859802781708726</v>
+        <v>0.1274555961397252</v>
       </c>
       <c r="V14">
-        <v>-1.295730186798176</v>
+        <v>0.1274555961397253</v>
       </c>
       <c r="W14">
-        <v>0.9859802781708726</v>
+        <v>0.1274555961397253</v>
       </c>
       <c r="X14">
-        <v>-121.2957301867982</v>
+        <v>0.1274555961397252</v>
       </c>
       <c r="Y14">
-        <v>0.9859802781708725</v>
+        <v>0.1274555961397253</v>
       </c>
       <c r="Z14">
-        <v>118.7042698132018</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
+        <v>0.1274555961397253</v>
+      </c>
+      <c r="AA14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI14">
+        <v>0.9862463452550615</v>
+      </c>
+      <c r="AJ14">
+        <v>-1.303432586369007</v>
+      </c>
+      <c r="AK14">
+        <v>0.9862463452550616</v>
+      </c>
+      <c r="AL14">
+        <v>-121.303432586369</v>
+      </c>
+      <c r="AM14">
+        <v>0.9862463452550615</v>
+      </c>
+      <c r="AN14">
+        <v>118.696567413631</v>
+      </c>
+      <c r="AO14">
+        <v>0.9828654806854344</v>
+      </c>
+      <c r="AP14">
+        <v>-1.634511253304505</v>
+      </c>
+      <c r="AQ14">
+        <v>0.9828654806854344</v>
+      </c>
+      <c r="AR14">
+        <v>-121.6345112533045</v>
+      </c>
+      <c r="AS14">
+        <v>0.9828654806854343</v>
+      </c>
+      <c r="AT14">
+        <v>118.3654887466955</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:52">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1844,22 +2744,22 @@
         <v>1.3</v>
       </c>
       <c r="C15">
-        <v>0.1706556790541588</v>
+        <v>0.2557876515525454</v>
       </c>
       <c r="D15">
-        <v>0.1706556790541588</v>
+        <v>0.2557876515525455</v>
       </c>
       <c r="E15">
-        <v>0.1706556790541588</v>
+        <v>0.2557876515525455</v>
       </c>
       <c r="F15">
-        <v>0.1706556790582643</v>
+        <v>0.1278938257798696</v>
       </c>
       <c r="G15">
-        <v>0.1706556790582643</v>
+        <v>0.1278938257798697</v>
       </c>
       <c r="H15">
-        <v>0.1706556790582643</v>
+        <v>0.1278938257798697</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1870,71 +2770,131 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
+      <c r="L15">
+        <v>0.1278938257798696</v>
+      </c>
+      <c r="M15">
+        <v>0.1278938257798697</v>
+      </c>
+      <c r="N15">
+        <v>0.1278938257798697</v>
       </c>
       <c r="O15">
-        <v>0.9905148770577104</v>
+        <v>0.3865866278581089</v>
       </c>
       <c r="P15">
-        <v>-0.8694950942052618</v>
+        <v>0.3865866278581088</v>
       </c>
       <c r="Q15">
-        <v>0.9905148770577102</v>
+        <v>0.3865866278581089</v>
       </c>
       <c r="R15">
-        <v>-120.8694950942052</v>
+        <v>0.1288622092919559</v>
       </c>
       <c r="S15">
-        <v>0.9905148770577102</v>
+        <v>0.1288622092919559</v>
       </c>
       <c r="T15">
-        <v>119.1305049057947</v>
+        <v>0.1288622092919559</v>
       </c>
       <c r="U15">
-        <v>0.9858235275464586</v>
+        <v>0.1288622092919559</v>
       </c>
       <c r="V15">
-        <v>-1.309830780919289</v>
+        <v>0.1288622092919559</v>
       </c>
       <c r="W15">
-        <v>0.9858235275464586</v>
+        <v>0.1288622092919559</v>
       </c>
       <c r="X15">
-        <v>-121.3098307809193</v>
+        <v>0.1288622092919559</v>
       </c>
       <c r="Y15">
-        <v>0.9858235275464585</v>
+        <v>0.1288622092919558</v>
       </c>
       <c r="Z15">
-        <v>118.6901692190807</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
+        <v>0.1288622092919559</v>
+      </c>
+      <c r="AA15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>0.9860900790398768</v>
+      </c>
+      <c r="AJ15">
+        <v>-1.317609380629713</v>
+      </c>
+      <c r="AK15">
+        <v>0.9860900790398768</v>
+      </c>
+      <c r="AL15">
+        <v>-121.3176093806297</v>
+      </c>
+      <c r="AM15">
+        <v>0.9860900790398767</v>
+      </c>
+      <c r="AN15">
+        <v>118.6823906193703</v>
+      </c>
+      <c r="AO15">
+        <v>0.9826719290013043</v>
+      </c>
+      <c r="AP15">
+        <v>-1.65235914089985</v>
+      </c>
+      <c r="AQ15">
+        <v>0.9826719290013044</v>
+      </c>
+      <c r="AR15">
+        <v>-121.6523591408999</v>
+      </c>
+      <c r="AS15">
+        <v>0.9826719290013043</v>
+      </c>
+      <c r="AT15">
+        <v>118.3476408591001</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
+    <row r="16" spans="1:52">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1942,22 +2902,22 @@
         <v>1.4</v>
       </c>
       <c r="C16">
-        <v>0.1724800863724269</v>
+        <v>0.2585323685083675</v>
       </c>
       <c r="D16">
-        <v>0.172480086372427</v>
+        <v>0.2585323685083676</v>
       </c>
       <c r="E16">
-        <v>0.172480086372427</v>
+        <v>0.2585323685083676</v>
       </c>
       <c r="F16">
-        <v>0.1724800863766686</v>
+        <v>0.129266184257884</v>
       </c>
       <c r="G16">
-        <v>0.1724800863766686</v>
+        <v>0.1292661842578841</v>
       </c>
       <c r="H16">
-        <v>0.1724800863766686</v>
+        <v>0.1292661842578841</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1968,71 +2928,131 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" t="b">
-        <v>1</v>
-      </c>
-      <c r="N16" t="b">
-        <v>0</v>
+      <c r="L16">
+        <v>0.1292661842578833</v>
+      </c>
+      <c r="M16">
+        <v>0.1292661842578833</v>
+      </c>
+      <c r="N16">
+        <v>0.1292661842578833</v>
       </c>
       <c r="O16">
-        <v>0.9904100281748831</v>
+        <v>0.3907700652001833</v>
       </c>
       <c r="P16">
-        <v>-0.8787210584866907</v>
+        <v>0.3907700652001834</v>
       </c>
       <c r="Q16">
-        <v>0.9904100281748831</v>
+        <v>0.3907700652001833</v>
       </c>
       <c r="R16">
-        <v>-120.8787210584867</v>
+        <v>0.1302566884061131</v>
       </c>
       <c r="S16">
-        <v>0.9904100281748831</v>
+        <v>0.1302566884061131</v>
       </c>
       <c r="T16">
-        <v>119.1212789415133</v>
+        <v>0.130256688406113</v>
       </c>
       <c r="U16">
-        <v>0.9856681129042683</v>
+        <v>0.1302566884061131</v>
       </c>
       <c r="V16">
-        <v>-1.323805896435099</v>
+        <v>0.1302566884061131</v>
       </c>
       <c r="W16">
-        <v>0.9856681129042681</v>
+        <v>0.1302566884061131</v>
       </c>
       <c r="X16">
-        <v>-121.3238058964351</v>
+        <v>0.1302566884061131</v>
       </c>
       <c r="Y16">
-        <v>0.9856681129042681</v>
+        <v>0.1302566884061131</v>
       </c>
       <c r="Z16">
-        <v>118.6761941035649</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
+        <v>0.1302566884061131</v>
+      </c>
+      <c r="AA16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>0.9859350998149795</v>
+      </c>
+      <c r="AJ16">
+        <v>-1.331660063978335</v>
+      </c>
+      <c r="AK16">
+        <v>0.9859350998149794</v>
+      </c>
+      <c r="AL16">
+        <v>-121.3316600639783</v>
+      </c>
+      <c r="AM16">
+        <v>0.9859350998149794</v>
+      </c>
+      <c r="AN16">
+        <v>118.6683399360217</v>
+      </c>
+      <c r="AO16">
+        <v>0.9824799892936976</v>
+      </c>
+      <c r="AP16">
+        <v>-1.670049707204335</v>
+      </c>
+      <c r="AQ16">
+        <v>0.9824799892936974</v>
+      </c>
+      <c r="AR16">
+        <v>-121.6700497072043</v>
+      </c>
+      <c r="AS16">
+        <v>0.9824799892936975</v>
+      </c>
+      <c r="AT16">
+        <v>118.3299502927956</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:52">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2040,22 +3060,22 @@
         <v>1.5</v>
       </c>
       <c r="C17">
-        <v>0.1742868360420642</v>
+        <v>0.2612507412125866</v>
       </c>
       <c r="D17">
-        <v>0.1742868360420643</v>
+        <v>0.2612507412125866</v>
       </c>
       <c r="E17">
-        <v>0.1742868360420643</v>
+        <v>0.2612507412125866</v>
       </c>
       <c r="F17">
-        <v>0.174286836046442</v>
+        <v>0.1306253706100974</v>
       </c>
       <c r="G17">
-        <v>0.1742868360464422</v>
+        <v>0.1306253706100974</v>
       </c>
       <c r="H17">
-        <v>0.1742868360464421</v>
+        <v>0.1306253706100974</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2066,71 +3086,131 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" t="b">
-        <v>0</v>
+      <c r="L17">
+        <v>0.1306253706100974</v>
+      </c>
+      <c r="M17">
+        <v>0.1306253706100974</v>
+      </c>
+      <c r="N17">
+        <v>0.1306253706100974</v>
       </c>
       <c r="O17">
-        <v>0.9903061421431014</v>
+        <v>0.3949141670844631</v>
       </c>
       <c r="P17">
-        <v>-0.8878567877593436</v>
+        <v>0.3949141670844631</v>
       </c>
       <c r="Q17">
-        <v>0.9903061421431013</v>
+        <v>0.3949141670844631</v>
       </c>
       <c r="R17">
-        <v>-120.8878567877593</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="S17">
-        <v>0.9903061421431013</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="T17">
-        <v>119.1121432122407</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="U17">
-        <v>0.9855141438111965</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="V17">
-        <v>-1.337645829263395</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="W17">
-        <v>0.9855141438111963</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="X17">
-        <v>-121.3376458292634</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="Y17">
-        <v>0.9855141438111964</v>
+        <v>0.1316380557009935</v>
       </c>
       <c r="Z17">
-        <v>118.6623541707366</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
+        <v>0.1316380557009935</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI17">
+        <v>0.9857815180358152</v>
+      </c>
+      <c r="AJ17">
+        <v>-1.345574880561216</v>
+      </c>
+      <c r="AK17">
+        <v>0.985781518035815</v>
+      </c>
+      <c r="AL17">
+        <v>-121.3455748805612</v>
+      </c>
+      <c r="AM17">
+        <v>0.9857815180358149</v>
+      </c>
+      <c r="AN17">
+        <v>118.6544251194388</v>
+      </c>
+      <c r="AO17">
+        <v>0.9822897978640655</v>
+      </c>
+      <c r="AP17">
+        <v>-1.687570630658231</v>
+      </c>
+      <c r="AQ17">
+        <v>0.9822897978640652</v>
+      </c>
+      <c r="AR17">
+        <v>-121.6875706306582</v>
+      </c>
+      <c r="AS17">
+        <v>0.9822897978640653</v>
+      </c>
+      <c r="AT17">
+        <v>118.3124293693418</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:52">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2138,22 +3218,22 @@
         <v>1.6</v>
       </c>
       <c r="C18">
-        <v>0.1760746724113036</v>
+        <v>0.2639408743428177</v>
       </c>
       <c r="D18">
-        <v>0.1760746724113036</v>
+        <v>0.2639408743428177</v>
       </c>
       <c r="E18">
-        <v>0.1760746724113036</v>
+        <v>0.2639408743428177</v>
       </c>
       <c r="F18">
-        <v>0.1760746724158245</v>
+        <v>0.1319704371753228</v>
       </c>
       <c r="G18">
-        <v>0.1760746724158245</v>
+        <v>0.1319704371753228</v>
       </c>
       <c r="H18">
-        <v>0.1760746724158245</v>
+        <v>0.1319704371753228</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2164,71 +3244,131 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
+      <c r="L18">
+        <v>0.1319704371753228</v>
+      </c>
+      <c r="M18">
+        <v>0.1319704371753228</v>
+      </c>
+      <c r="N18">
+        <v>0.1319704371753228</v>
       </c>
       <c r="O18">
-        <v>0.9902032927307285</v>
+        <v>0.3990160223302716</v>
       </c>
       <c r="P18">
-        <v>-0.8968959610586459</v>
+        <v>0.3990160223302716</v>
       </c>
       <c r="Q18">
-        <v>0.9902032927307284</v>
+        <v>0.3990160223302715</v>
       </c>
       <c r="R18">
-        <v>-120.8968959610586</v>
+        <v>0.1330053407830548</v>
       </c>
       <c r="S18">
-        <v>0.9902032927307285</v>
+        <v>0.1330053407830547</v>
       </c>
       <c r="T18">
-        <v>119.1031040389413</v>
+        <v>0.1330053407830547</v>
       </c>
       <c r="U18">
-        <v>0.9853617290425237</v>
+        <v>0.1330053407830547</v>
       </c>
       <c r="V18">
-        <v>-1.351340959471384</v>
+        <v>0.1330053407830547</v>
       </c>
       <c r="W18">
-        <v>0.9853617290425238</v>
+        <v>0.1330053407830547</v>
       </c>
       <c r="X18">
-        <v>-121.3513409594714</v>
+        <v>0.1330053407830547</v>
       </c>
       <c r="Y18">
-        <v>0.9853617290425237</v>
+        <v>0.1330053407830547</v>
       </c>
       <c r="Z18">
-        <v>118.6486590405286</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
+        <v>0.1330053407830547</v>
+      </c>
+      <c r="AA18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI18">
+        <v>0.9856294434817134</v>
+      </c>
+      <c r="AJ18">
+        <v>-1.35934415890085</v>
+      </c>
+      <c r="AK18">
+        <v>0.9856294434817133</v>
+      </c>
+      <c r="AL18">
+        <v>-121.3593441589008</v>
+      </c>
+      <c r="AM18">
+        <v>0.9856294434817136</v>
+      </c>
+      <c r="AN18">
+        <v>118.6406558410991</v>
+      </c>
+      <c r="AO18">
+        <v>0.9821014901324073</v>
+      </c>
+      <c r="AP18">
+        <v>-1.704909692273519</v>
+      </c>
+      <c r="AQ18">
+        <v>0.9821014901324071</v>
+      </c>
+      <c r="AR18">
+        <v>-121.7049096922735</v>
+      </c>
+      <c r="AS18">
+        <v>0.9821014901324072</v>
+      </c>
+      <c r="AT18">
+        <v>118.2950903077265</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" spans="1:52">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2236,22 +3376,22 @@
         <v>1.7</v>
       </c>
       <c r="C19">
-        <v>0.1778423517518909</v>
+        <v>0.2666008899501551</v>
       </c>
       <c r="D19">
-        <v>0.1778423517518909</v>
+        <v>0.2666008899501552</v>
       </c>
       <c r="E19">
-        <v>0.1778423517518909</v>
+        <v>0.2666008899501552</v>
       </c>
       <c r="F19">
-        <v>0.1778423517565471</v>
+        <v>0.1333004449791044</v>
       </c>
       <c r="G19">
-        <v>0.1778423517565471</v>
+        <v>0.1333004449791044</v>
       </c>
       <c r="H19">
-        <v>0.1778423517565471</v>
+        <v>0.1333004449791044</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2262,71 +3402,131 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="L19" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
+      <c r="L19">
+        <v>0.1333004449791044</v>
+      </c>
+      <c r="M19">
+        <v>0.1333004449791044</v>
+      </c>
+      <c r="N19">
+        <v>0.1333004449791044</v>
       </c>
       <c r="O19">
-        <v>0.9901015531455419</v>
+        <v>0.4030727440942727</v>
       </c>
       <c r="P19">
-        <v>-0.9058323199913475</v>
+        <v>0.4030727440942727</v>
       </c>
       <c r="Q19">
-        <v>0.9901015531455418</v>
+        <v>0.4030727440942728</v>
       </c>
       <c r="R19">
-        <v>-120.9058323199914</v>
+        <v>0.1343575813711758</v>
       </c>
       <c r="S19">
-        <v>0.9901015531455416</v>
+        <v>0.1343575813711758</v>
       </c>
       <c r="T19">
-        <v>119.0941676800087</v>
+        <v>0.1343575813711758</v>
       </c>
       <c r="U19">
-        <v>0.9852109764987288</v>
+        <v>0.1343575813711758</v>
       </c>
       <c r="V19">
-        <v>-1.364881758222389</v>
+        <v>0.1343575813711758</v>
       </c>
       <c r="W19">
-        <v>0.9852109764987287</v>
+        <v>0.1343575813711758</v>
       </c>
       <c r="X19">
-        <v>-121.3648817582224</v>
+        <v>0.1343575813711759</v>
       </c>
       <c r="Y19">
-        <v>0.9852109764987287</v>
+        <v>0.1343575813711758</v>
       </c>
       <c r="Z19">
-        <v>118.6351182417776</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
+        <v>0.1343575813711758</v>
+      </c>
+      <c r="AA19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI19">
+        <v>0.9854789851687346</v>
+      </c>
+      <c r="AJ19">
+        <v>-1.372958318874216</v>
+      </c>
+      <c r="AK19">
+        <v>0.9854789851687346</v>
+      </c>
+      <c r="AL19">
+        <v>-121.3729583188742</v>
+      </c>
+      <c r="AM19">
+        <v>0.9854789851687344</v>
+      </c>
+      <c r="AN19">
+        <v>118.6270416811258</v>
+      </c>
+      <c r="AO19">
+        <v>0.9819152005311114</v>
+      </c>
+      <c r="AP19">
+        <v>-1.722054784554625</v>
+      </c>
+      <c r="AQ19">
+        <v>0.9819152005311113</v>
+      </c>
+      <c r="AR19">
+        <v>-121.7220547845546</v>
+      </c>
+      <c r="AS19">
+        <v>0.981915200531111</v>
+      </c>
+      <c r="AT19">
+        <v>118.2779452154454</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:52">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2334,22 +3534,22 @@
         <v>1.8</v>
       </c>
       <c r="C20">
-        <v>0.1795886431604491</v>
+        <v>0.2692289288363461</v>
       </c>
       <c r="D20">
-        <v>0.1795886431604492</v>
+        <v>0.2692289288363461</v>
       </c>
       <c r="E20">
-        <v>0.1795886431604492</v>
+        <v>0.2692289288363461</v>
       </c>
       <c r="F20">
-        <v>0.1795886431652393</v>
+        <v>0.1346144644223004</v>
       </c>
       <c r="G20">
-        <v>0.1795886431652395</v>
+        <v>0.1346144644223004</v>
       </c>
       <c r="H20">
-        <v>0.1795886431652394</v>
+        <v>0.1346144644223004</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2360,71 +3560,131 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" t="b">
-        <v>0</v>
+      <c r="L20">
+        <v>0.1346144644223004</v>
+      </c>
+      <c r="M20">
+        <v>0.1346144644223004</v>
+      </c>
+      <c r="N20">
+        <v>0.1346144644223004</v>
       </c>
       <c r="O20">
-        <v>0.9900009959772811</v>
+        <v>0.4070814720429603</v>
       </c>
       <c r="P20">
-        <v>-0.9146596731929871</v>
+        <v>0.4070814720429604</v>
       </c>
       <c r="Q20">
-        <v>0.990000995977281</v>
+        <v>0.4070814720429603</v>
       </c>
       <c r="R20">
-        <v>-120.914659673193</v>
+        <v>0.1356938240208542</v>
       </c>
       <c r="S20">
-        <v>0.990000995977281</v>
+        <v>0.1356938240208543</v>
       </c>
       <c r="T20">
-        <v>119.085340326807</v>
+        <v>0.1356938240208542</v>
       </c>
       <c r="U20">
-        <v>0.9850619931223308</v>
+        <v>0.1356938240208542</v>
       </c>
       <c r="V20">
-        <v>-1.378258794684954</v>
+        <v>0.1356938240208543</v>
       </c>
       <c r="W20">
-        <v>0.9850619931223307</v>
+        <v>0.1356938240208543</v>
       </c>
       <c r="X20">
-        <v>-121.3782587946849</v>
+        <v>0.1356938240208542</v>
       </c>
       <c r="Y20">
-        <v>0.9850619931223307</v>
+        <v>0.1356938240208543</v>
       </c>
       <c r="Z20">
-        <v>118.621741205315</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
+        <v>0.1356938240208543</v>
+      </c>
+      <c r="AA20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI20">
+        <v>0.9853302512622237</v>
+      </c>
+      <c r="AJ20">
+        <v>-1.386407878654207</v>
+      </c>
+      <c r="AK20">
+        <v>0.9853302512622238</v>
+      </c>
+      <c r="AL20">
+        <v>-121.3864078786542</v>
+      </c>
+      <c r="AM20">
+        <v>0.9853302512622236</v>
+      </c>
+      <c r="AN20">
+        <v>118.6135921213458</v>
+      </c>
+      <c r="AO20">
+        <v>0.9817310623985547</v>
+      </c>
+      <c r="AP20">
+        <v>-1.738993920383143</v>
+      </c>
+      <c r="AQ20">
+        <v>0.9817310623985545</v>
+      </c>
+      <c r="AR20">
+        <v>-121.7389939203831</v>
+      </c>
+      <c r="AS20">
+        <v>0.9817310623985545</v>
+      </c>
+      <c r="AT20">
+        <v>118.2610060796168</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:52">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2432,22 +3692,22 @@
         <v>1.9</v>
       </c>
       <c r="C21">
-        <v>0.1813123294540719</v>
+        <v>0.2718231519239216</v>
       </c>
       <c r="D21">
-        <v>0.1813123294540719</v>
+        <v>0.2718231519239217</v>
       </c>
       <c r="E21">
-        <v>0.181312329454072</v>
+        <v>0.2718231519239217</v>
       </c>
       <c r="F21">
-        <v>0.1813123294590102</v>
+        <v>0.1359115759662003</v>
       </c>
       <c r="G21">
-        <v>0.1813123294590102</v>
+        <v>0.1359115759662004</v>
       </c>
       <c r="H21">
-        <v>0.1813123294590102</v>
+        <v>0.1359115759662004</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2458,71 +3718,131 @@
       <c r="K21">
         <v>0</v>
       </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" t="b">
-        <v>1</v>
-      </c>
-      <c r="N21" t="b">
-        <v>0</v>
+      <c r="L21">
+        <v>0.1359115759662003</v>
+      </c>
+      <c r="M21">
+        <v>0.1359115759662004</v>
+      </c>
+      <c r="N21">
+        <v>0.1359115759662004</v>
       </c>
       <c r="O21">
-        <v>0.9899016931401919</v>
+        <v>0.411039374521093</v>
       </c>
       <c r="P21">
-        <v>-0.9233719007497385</v>
+        <v>0.4110393745210931</v>
       </c>
       <c r="Q21">
-        <v>0.9899016931401918</v>
+        <v>0.411039374521093</v>
       </c>
       <c r="R21">
-        <v>-120.9233719007497</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="S21">
-        <v>0.9899016931401919</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="T21">
-        <v>119.0766280992503</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="U21">
-        <v>0.984914884814846</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="V21">
-        <v>-1.391462742898403</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="W21">
-        <v>0.9849148848148458</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="X21">
-        <v>-121.3914627428984</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="Y21">
-        <v>0.9849148848148459</v>
+        <v>0.1370131248470153</v>
       </c>
       <c r="Z21">
-        <v>118.6085372571016</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
+        <v>0.1370131248470153</v>
+      </c>
+      <c r="AA21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI21">
+        <v>0.9851833489891918</v>
+      </c>
+      <c r="AJ21">
+        <v>-1.39968346160884</v>
+      </c>
+      <c r="AK21">
+        <v>0.9851833489891916</v>
+      </c>
+      <c r="AL21">
+        <v>-121.3996834616088</v>
+      </c>
+      <c r="AM21">
+        <v>0.9851833489891917</v>
+      </c>
+      <c r="AN21">
+        <v>118.6003165383911</v>
+      </c>
+      <c r="AO21">
+        <v>0.9815492078725847</v>
+      </c>
+      <c r="AP21">
+        <v>-1.755715241859515</v>
+      </c>
+      <c r="AQ21">
+        <v>0.9815492078725846</v>
+      </c>
+      <c r="AR21">
+        <v>-121.7557152418595</v>
+      </c>
+      <c r="AS21">
+        <v>0.9815492078725846</v>
+      </c>
+      <c r="AT21">
+        <v>118.2442847581405</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" spans="1:52">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2530,22 +3850,22 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>0.183012208059325</v>
+        <v>0.2743817416181468</v>
       </c>
       <c r="D22">
-        <v>0.183012208059325</v>
+        <v>0.2743817416181469</v>
       </c>
       <c r="E22">
-        <v>0.183012208059325</v>
+        <v>0.2743817416181469</v>
       </c>
       <c r="F22">
-        <v>0.1830122080644054</v>
+        <v>0.1371908708134161</v>
       </c>
       <c r="G22">
-        <v>0.1830122080644054</v>
+        <v>0.1371908708134162</v>
       </c>
       <c r="H22">
-        <v>0.1830122080644054</v>
+        <v>0.1371908708134162</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2556,67 +3876,127 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" t="b">
-        <v>1</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
+      <c r="L22">
+        <v>0.1371908708134161</v>
+      </c>
+      <c r="M22">
+        <v>0.1371908708134162</v>
+      </c>
+      <c r="N22">
+        <v>0.1371908708134162</v>
       </c>
       <c r="O22">
-        <v>0.9898037158156341</v>
+        <v>0.414943650714382</v>
       </c>
       <c r="P22">
-        <v>-0.9319629585812073</v>
+        <v>0.4149436507143819</v>
       </c>
       <c r="Q22">
-        <v>0.9898037158156341</v>
+        <v>0.414943650714382</v>
       </c>
       <c r="R22">
-        <v>-120.9319629585812</v>
+        <v>0.1383145502448935</v>
       </c>
       <c r="S22">
-        <v>0.9898037158156339</v>
+        <v>0.1383145502448935</v>
       </c>
       <c r="T22">
-        <v>119.0680370414188</v>
+        <v>0.1383145502448935</v>
       </c>
       <c r="U22">
-        <v>0.9847697563539631</v>
+        <v>0.1383145502448935</v>
       </c>
       <c r="V22">
-        <v>-1.404484388589012</v>
+        <v>0.1383145502448935</v>
       </c>
       <c r="W22">
-        <v>0.9847697563539631</v>
+        <v>0.1383145502448935</v>
       </c>
       <c r="X22">
-        <v>-121.404484388589</v>
+        <v>0.1383145502448942</v>
       </c>
       <c r="Y22">
-        <v>0.9847697563539631</v>
+        <v>0.1383145502448942</v>
       </c>
       <c r="Z22">
-        <v>118.595515611411</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
+        <v>0.1383145502448942</v>
+      </c>
+      <c r="AA22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI22">
+        <v>0.9850383845505831</v>
+      </c>
+      <c r="AJ22">
+        <v>-1.412775803152303</v>
+      </c>
+      <c r="AK22">
+        <v>0.9850383845505829</v>
+      </c>
+      <c r="AL22">
+        <v>-121.4127758031523</v>
+      </c>
+      <c r="AM22">
+        <v>0.9850383845505829</v>
+      </c>
+      <c r="AN22">
+        <v>118.5872241968477</v>
+      </c>
+      <c r="AO22">
+        <v>0.9813697677839976</v>
+      </c>
+      <c r="AP22">
+        <v>-1.772207029093641</v>
+      </c>
+      <c r="AQ22">
+        <v>0.9813697677839975</v>
+      </c>
+      <c r="AR22">
+        <v>-121.7722070290936</v>
+      </c>
+      <c r="AS22">
+        <v>0.9813697677839975</v>
+      </c>
+      <c r="AT22">
+        <v>118.2277929709063</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
         <v>0</v>
       </c>
     </row>
